--- a/expense_dashboard/input/ExpenseTracker.xlsx
+++ b/expense_dashboard/input/ExpenseTracker.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\2026 Annual Documentation\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ws_openai\codex_projects\expense_dashboard\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_0454703C0185EDA9C35A8612C04ADB1C5665F969" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D4E9544-DC36-4820-B019-9ADD51C60890}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="358" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>Date</t>
   </si>
@@ -44,312 +44,6 @@
   </si>
   <si>
     <t>Receipt Link</t>
-  </si>
-  <si>
-    <t>Groceries</t>
-  </si>
-  <si>
-    <t>Publix</t>
-  </si>
-  <si>
-    <t>Whole Foods Market</t>
-  </si>
-  <si>
-    <t>Rent</t>
-  </si>
-  <si>
-    <t>Solace Timacuan</t>
-  </si>
-  <si>
-    <t>Meals</t>
-  </si>
-  <si>
-    <t>Giovannis</t>
-  </si>
-  <si>
-    <t>Auto Loan</t>
-  </si>
-  <si>
-    <t>TD Auto Finance</t>
-  </si>
-  <si>
-    <t>Streaming</t>
-  </si>
-  <si>
-    <t>SiriusXM</t>
-  </si>
-  <si>
-    <t>UTIL - Electric</t>
-  </si>
-  <si>
-    <t>FPL</t>
-  </si>
-  <si>
-    <t>Job</t>
-  </si>
-  <si>
-    <t>SquareSpace - Personal Website</t>
-  </si>
-  <si>
-    <t>Moving - Supplies</t>
-  </si>
-  <si>
-    <t>SidioCrate</t>
-  </si>
-  <si>
-    <t>Personal Care</t>
-  </si>
-  <si>
-    <t>Blissal Exfoliating Antibacterial Shower Towle</t>
-  </si>
-  <si>
-    <t>Moving - Storage</t>
-  </si>
-  <si>
-    <t>Extra Space Storage</t>
-  </si>
-  <si>
-    <t>Finance</t>
-  </si>
-  <si>
-    <t>FINVIZ - API Service</t>
-  </si>
-  <si>
-    <t>Alienware 18 Area-51 Laptop</t>
-  </si>
-  <si>
-    <t>Movie</t>
-  </si>
-  <si>
-    <t>Predator - Badlands</t>
-  </si>
-  <si>
-    <t>Options Guide</t>
-  </si>
-  <si>
-    <t>IRS</t>
-  </si>
-  <si>
-    <t>2024_IRS_PLAN</t>
-  </si>
-  <si>
-    <t>Student Loans</t>
-  </si>
-  <si>
-    <t>Mohela</t>
-  </si>
-  <si>
-    <t>2024 Microsoft Home Office Products</t>
-  </si>
-  <si>
-    <t>Moving - Transportation</t>
-  </si>
-  <si>
-    <t>UHaul</t>
-  </si>
-  <si>
-    <t>Entertainment</t>
-  </si>
-  <si>
-    <t>Reframe Your Brain - Scott Adams</t>
-  </si>
-  <si>
-    <t>Dust Bunny</t>
-  </si>
-  <si>
-    <t>UTIL - Internet</t>
-  </si>
-  <si>
-    <t>Spectrum</t>
-  </si>
-  <si>
-    <t>NetFlix</t>
-  </si>
-  <si>
-    <t>Peacock</t>
-  </si>
-  <si>
-    <t>Insurance - Auto</t>
-  </si>
-  <si>
-    <t>Progressive</t>
-  </si>
-  <si>
-    <t>UTIL - Phone</t>
-  </si>
-  <si>
-    <t>Verizon</t>
-  </si>
-  <si>
-    <t>UTIL - Water</t>
-  </si>
-  <si>
-    <t>Uber</t>
-  </si>
-  <si>
-    <t>Sling</t>
-  </si>
-  <si>
-    <t>Credit Card</t>
-  </si>
-  <si>
-    <t>CapitalOne</t>
-  </si>
-  <si>
-    <t>FairWinds Credit Union</t>
-  </si>
-  <si>
-    <t>OrthoFeet</t>
-  </si>
-  <si>
-    <t>Insurance - Renters</t>
-  </si>
-  <si>
-    <t>StateFarm</t>
-  </si>
-  <si>
-    <t>UPS</t>
-  </si>
-  <si>
-    <t>Insurance - Whole Life</t>
-  </si>
-  <si>
-    <t>AIApply</t>
-  </si>
-  <si>
-    <t>ATT</t>
-  </si>
-  <si>
-    <t>Moving - Lodging</t>
-  </si>
-  <si>
-    <t>WoodSpring Suites - Bradenton</t>
-  </si>
-  <si>
-    <t>Marine Laboratory &amp; Aquarium</t>
-  </si>
-  <si>
-    <t>ESA Select Suites - Kissimmee</t>
-  </si>
-  <si>
-    <t>Finance Research</t>
-  </si>
-  <si>
-    <t>Panera Bread</t>
-  </si>
-  <si>
-    <t>ESA Select Suites - Alamonte Springs</t>
-  </si>
-  <si>
-    <t>Jets Pizza</t>
-  </si>
-  <si>
-    <t>Cracker Barrel</t>
-  </si>
-  <si>
-    <t>Denny's</t>
-  </si>
-  <si>
-    <t>Pei Wei Asian Kitchen</t>
-  </si>
-  <si>
-    <t>Gas</t>
-  </si>
-  <si>
-    <t>7-Eleven</t>
-  </si>
-  <si>
-    <t>Starbucks</t>
-  </si>
-  <si>
-    <t>Denny's Restaurant #7947</t>
-  </si>
-  <si>
-    <t>Clothing</t>
-  </si>
-  <si>
-    <t>Bass Pro Shops</t>
-  </si>
-  <si>
-    <t>WoodSpring Suites - Jacksonville</t>
-  </si>
-  <si>
-    <t>Maple Street Biscuit Company</t>
-  </si>
-  <si>
-    <t>4 Rivers Smokehouse</t>
-  </si>
-  <si>
-    <t>Marco's Pizza</t>
-  </si>
-  <si>
-    <t>Marcos Pizza</t>
-  </si>
-  <si>
-    <t>Culver's</t>
-  </si>
-  <si>
-    <t>Shell</t>
-  </si>
-  <si>
-    <t>Winn-Dixie</t>
-  </si>
-  <si>
-    <t>Trust &amp; Will</t>
-  </si>
-  <si>
-    <t>MO</t>
-  </si>
-  <si>
-    <t>First Watch</t>
-  </si>
-  <si>
-    <t>Starbucks Store #11387</t>
-  </si>
-  <si>
-    <t>AMC Theatres</t>
-  </si>
-  <si>
-    <t>Amazon Prime</t>
-  </si>
-  <si>
-    <t>Winn Dixie</t>
-  </si>
-  <si>
-    <t>Bass Pro Shops Outdoor World</t>
-  </si>
-  <si>
-    <t>Newk's Eatery</t>
-  </si>
-  <si>
-    <t>Texas Roadhouse</t>
-  </si>
-  <si>
-    <t>ESA Select Suites - Jacksonville - North</t>
-  </si>
-  <si>
-    <t>Literature</t>
-  </si>
-  <si>
-    <t>A Fractured IT - BrightKey Press Release</t>
-  </si>
-  <si>
-    <t>Stoners Pizza</t>
-  </si>
-  <si>
-    <t>Tous Les Jours</t>
-  </si>
-  <si>
-    <t>Elite Nail Spa</t>
-  </si>
-  <si>
-    <t>Arbys</t>
-  </si>
-  <si>
-    <t>A Fractured IT - Book Funnel</t>
-  </si>
-  <si>
-    <t>OpenAI OpCo, LLC</t>
   </si>
 </sst>
 </file>
@@ -775,27 +469,13 @@
       <c r="Z1" s="4"/>
     </row>
     <row r="2" spans="1:26">
-      <c r="A2" s="5">
-        <v>45894</v>
-      </c>
-      <c r="B2" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="D2" s="7">
-        <v>137.58000000000001</v>
-      </c>
-      <c r="E2" s="7">
-        <v>1.82</v>
-      </c>
-      <c r="F2" s="7">
-        <v>139.4</v>
-      </c>
-      <c r="G2" s="7">
-        <v>0</v>
-      </c>
+      <c r="A2" s="5"/>
+      <c r="B2" s="6"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="7"/>
+      <c r="E2" s="7"/>
+      <c r="F2" s="7"/>
+      <c r="G2" s="7"/>
       <c r="H2" s="6"/>
       <c r="I2" s="4"/>
       <c r="J2" s="4"/>
@@ -817,27 +497,13 @@
       <c r="Z2" s="4"/>
     </row>
     <row r="3" spans="1:26">
-      <c r="A3" s="5">
-        <v>45935</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="D3" s="7">
-        <v>104.82</v>
-      </c>
-      <c r="E3" s="7">
-        <v>2.25</v>
-      </c>
-      <c r="F3" s="7">
-        <v>103.69</v>
-      </c>
-      <c r="G3" s="7">
-        <v>0</v>
-      </c>
+      <c r="A3" s="5"/>
+      <c r="B3" s="6"/>
+      <c r="C3" s="6"/>
+      <c r="D3" s="7"/>
+      <c r="E3" s="7"/>
+      <c r="F3" s="7"/>
+      <c r="G3" s="7"/>
       <c r="H3" s="6"/>
       <c r="I3" s="4"/>
       <c r="J3" s="4"/>
@@ -859,50 +525,22 @@
       <c r="Z3" s="4"/>
     </row>
     <row r="4" spans="1:26">
-      <c r="A4" s="8">
-        <v>46023</v>
-      </c>
-      <c r="B4" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="D4" s="10">
-        <v>1828.18</v>
-      </c>
-      <c r="E4" s="7">
-        <v>0</v>
-      </c>
-      <c r="F4" s="10">
-        <v>1828.18</v>
-      </c>
-      <c r="G4" s="7">
-        <v>0</v>
-      </c>
+      <c r="A4" s="8"/>
+      <c r="B4" s="9"/>
+      <c r="C4" s="9"/>
+      <c r="D4" s="10"/>
+      <c r="E4" s="7"/>
+      <c r="F4" s="10"/>
+      <c r="G4" s="7"/>
     </row>
     <row r="5" spans="1:26">
-      <c r="A5" s="11">
-        <v>46024</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="D5" s="7">
-        <v>36.99</v>
-      </c>
-      <c r="E5" s="7">
-        <v>2.59</v>
-      </c>
-      <c r="F5" s="7">
-        <v>46.24</v>
-      </c>
-      <c r="G5" s="7">
-        <v>6.66</v>
-      </c>
+      <c r="A5" s="11"/>
+      <c r="B5" s="6"/>
+      <c r="C5" s="6"/>
+      <c r="D5" s="7"/>
+      <c r="E5" s="7"/>
+      <c r="F5" s="7"/>
+      <c r="G5" s="7"/>
       <c r="H5" s="6"/>
       <c r="I5" s="4"/>
       <c r="J5" s="4"/>
@@ -924,27 +562,13 @@
       <c r="Z5" s="4"/>
     </row>
     <row r="6" spans="1:26">
-      <c r="A6" s="11">
-        <v>46024</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="D6" s="10">
-        <v>886.7</v>
-      </c>
-      <c r="E6" s="7">
-        <v>0</v>
-      </c>
-      <c r="F6" s="10">
-        <v>886.7</v>
-      </c>
-      <c r="G6" s="7">
-        <v>0</v>
-      </c>
+      <c r="A6" s="11"/>
+      <c r="B6" s="6"/>
+      <c r="C6" s="6"/>
+      <c r="D6" s="10"/>
+      <c r="E6" s="7"/>
+      <c r="F6" s="10"/>
+      <c r="G6" s="7"/>
       <c r="H6" s="6"/>
       <c r="I6" s="12"/>
       <c r="J6" s="4"/>
@@ -966,27 +590,13 @@
       <c r="Z6" s="4"/>
     </row>
     <row r="7" spans="1:26">
-      <c r="A7" s="11">
-        <v>46024</v>
-      </c>
-      <c r="B7" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="C7" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="D7" s="14">
-        <v>28.29</v>
-      </c>
-      <c r="E7" s="7">
-        <v>0</v>
-      </c>
-      <c r="F7" s="14">
-        <v>28.29</v>
-      </c>
-      <c r="G7" s="7">
-        <v>0</v>
-      </c>
+      <c r="A7" s="11"/>
+      <c r="B7" s="12"/>
+      <c r="C7" s="13"/>
+      <c r="D7" s="14"/>
+      <c r="E7" s="7"/>
+      <c r="F7" s="14"/>
+      <c r="G7" s="7"/>
       <c r="H7" s="6"/>
       <c r="I7" s="4"/>
       <c r="J7" s="4"/>
@@ -1008,27 +618,13 @@
       <c r="Z7" s="4"/>
     </row>
     <row r="8" spans="1:26">
-      <c r="A8" s="11">
-        <v>46026</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="D8" s="7">
-        <v>193.83</v>
-      </c>
-      <c r="E8" s="7">
-        <v>0</v>
-      </c>
-      <c r="F8" s="7">
-        <v>193.83</v>
-      </c>
-      <c r="G8" s="7">
-        <v>0</v>
-      </c>
+      <c r="A8" s="11"/>
+      <c r="B8" s="6"/>
+      <c r="C8" s="6"/>
+      <c r="D8" s="7"/>
+      <c r="E8" s="7"/>
+      <c r="F8" s="7"/>
+      <c r="G8" s="7"/>
       <c r="H8" s="6"/>
       <c r="I8" s="4"/>
       <c r="J8" s="4"/>
@@ -1050,27 +646,13 @@
       <c r="Z8" s="4"/>
     </row>
     <row r="9" spans="1:26">
-      <c r="A9" s="11">
-        <v>46026</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="D9" s="7">
-        <v>47.95</v>
-      </c>
-      <c r="E9" s="7">
-        <v>3.36</v>
-      </c>
-      <c r="F9" s="7">
-        <v>59.94</v>
-      </c>
-      <c r="G9" s="7">
-        <v>8.6300000000000008</v>
-      </c>
+      <c r="A9" s="11"/>
+      <c r="B9" s="6"/>
+      <c r="C9" s="6"/>
+      <c r="D9" s="7"/>
+      <c r="E9" s="7"/>
+      <c r="F9" s="7"/>
+      <c r="G9" s="7"/>
       <c r="H9" s="6"/>
       <c r="I9" s="4"/>
       <c r="J9" s="4"/>
@@ -1092,27 +674,13 @@
       <c r="Z9" s="4"/>
     </row>
     <row r="10" spans="1:26">
-      <c r="A10" s="11">
-        <v>46027</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="D10" s="14">
-        <v>36</v>
-      </c>
-      <c r="E10" s="7">
-        <v>0</v>
-      </c>
-      <c r="F10" s="14">
-        <v>36</v>
-      </c>
-      <c r="G10" s="7">
-        <v>0</v>
-      </c>
+      <c r="A10" s="11"/>
+      <c r="B10" s="6"/>
+      <c r="C10" s="6"/>
+      <c r="D10" s="14"/>
+      <c r="E10" s="7"/>
+      <c r="F10" s="14"/>
+      <c r="G10" s="7"/>
       <c r="H10" s="6"/>
       <c r="I10" s="4"/>
       <c r="J10" s="4"/>
@@ -1134,27 +702,13 @@
       <c r="Z10" s="4"/>
     </row>
     <row r="11" spans="1:26">
-      <c r="A11" s="11">
-        <v>46028</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="C11" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="D11" s="7">
-        <v>79.989999999999995</v>
-      </c>
-      <c r="E11" s="7">
-        <v>0</v>
-      </c>
-      <c r="F11" s="7">
-        <v>79.989999999999995</v>
-      </c>
-      <c r="G11" s="7">
-        <v>0</v>
-      </c>
+      <c r="A11" s="11"/>
+      <c r="B11" s="6"/>
+      <c r="C11" s="6"/>
+      <c r="D11" s="7"/>
+      <c r="E11" s="7"/>
+      <c r="F11" s="7"/>
+      <c r="G11" s="7"/>
       <c r="H11" s="6"/>
       <c r="I11" s="4"/>
       <c r="J11" s="4"/>
@@ -1176,27 +730,13 @@
       <c r="Z11" s="4"/>
     </row>
     <row r="12" spans="1:26">
-      <c r="A12" s="11">
-        <v>46030</v>
-      </c>
-      <c r="B12" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C12" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="D12" s="7">
-        <v>35.94</v>
-      </c>
-      <c r="E12" s="7">
-        <v>0</v>
-      </c>
-      <c r="F12" s="7">
-        <v>35.94</v>
-      </c>
-      <c r="G12" s="7">
-        <v>0</v>
-      </c>
+      <c r="A12" s="11"/>
+      <c r="B12" s="6"/>
+      <c r="C12" s="6"/>
+      <c r="D12" s="7"/>
+      <c r="E12" s="7"/>
+      <c r="F12" s="7"/>
+      <c r="G12" s="7"/>
       <c r="H12" s="6"/>
       <c r="I12" s="4"/>
       <c r="J12" s="4"/>
@@ -1218,27 +758,13 @@
       <c r="Z12" s="4"/>
     </row>
     <row r="13" spans="1:26">
-      <c r="A13" s="15">
-        <v>46030</v>
-      </c>
-      <c r="B13" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="C13" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="D13" s="16">
-        <v>195.47</v>
-      </c>
-      <c r="E13" s="16">
-        <v>0</v>
-      </c>
-      <c r="F13" s="16">
-        <v>195.47</v>
-      </c>
-      <c r="G13" s="16">
-        <v>0</v>
-      </c>
+      <c r="A13" s="15"/>
+      <c r="B13" s="12"/>
+      <c r="C13" s="12"/>
+      <c r="D13" s="16"/>
+      <c r="E13" s="16"/>
+      <c r="F13" s="16"/>
+      <c r="G13" s="16"/>
       <c r="H13" s="17"/>
       <c r="I13" s="4"/>
       <c r="J13" s="4"/>
@@ -1260,27 +786,13 @@
       <c r="Z13" s="4"/>
     </row>
     <row r="14" spans="1:26">
-      <c r="A14" s="15">
-        <v>46030</v>
-      </c>
-      <c r="B14" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="C14" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="D14" s="14">
-        <v>39.799999999999997</v>
-      </c>
-      <c r="E14" s="16">
-        <v>0</v>
-      </c>
-      <c r="F14" s="14">
-        <v>39.799999999999997</v>
-      </c>
-      <c r="G14" s="16">
-        <v>0</v>
-      </c>
+      <c r="A14" s="15"/>
+      <c r="B14" s="12"/>
+      <c r="C14" s="12"/>
+      <c r="D14" s="14"/>
+      <c r="E14" s="16"/>
+      <c r="F14" s="14"/>
+      <c r="G14" s="16"/>
       <c r="H14" s="17"/>
       <c r="I14" s="4"/>
       <c r="J14" s="4"/>
@@ -1302,27 +814,13 @@
       <c r="Z14" s="4"/>
     </row>
     <row r="15" spans="1:26">
-      <c r="A15" s="15">
-        <v>46031</v>
-      </c>
-      <c r="B15" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="C15" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="D15" s="16">
-        <v>2979.97</v>
-      </c>
-      <c r="E15" s="16">
-        <v>187.59</v>
-      </c>
-      <c r="F15" s="16">
-        <v>2867.56</v>
-      </c>
-      <c r="G15" s="16">
-        <v>0</v>
-      </c>
+      <c r="A15" s="15"/>
+      <c r="B15" s="6"/>
+      <c r="C15" s="12"/>
+      <c r="D15" s="16"/>
+      <c r="E15" s="16"/>
+      <c r="F15" s="16"/>
+      <c r="G15" s="16"/>
       <c r="H15" s="17"/>
       <c r="I15" s="4"/>
       <c r="J15" s="4"/>
@@ -1344,27 +842,13 @@
       <c r="Z15" s="4"/>
     </row>
     <row r="16" spans="1:26">
-      <c r="A16" s="15">
-        <v>46031</v>
-      </c>
-      <c r="B16" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="C16" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="D16" s="16">
-        <v>24.99</v>
-      </c>
-      <c r="E16" s="16">
-        <v>3.76</v>
-      </c>
-      <c r="F16" s="16">
-        <v>28.75</v>
-      </c>
-      <c r="G16" s="16">
-        <v>0</v>
-      </c>
+      <c r="A16" s="15"/>
+      <c r="B16" s="12"/>
+      <c r="C16" s="12"/>
+      <c r="D16" s="16"/>
+      <c r="E16" s="16"/>
+      <c r="F16" s="16"/>
+      <c r="G16" s="16"/>
       <c r="H16" s="17"/>
       <c r="I16" s="4"/>
       <c r="J16" s="4"/>
@@ -1386,27 +870,13 @@
       <c r="Z16" s="4"/>
     </row>
     <row r="17" spans="1:26">
-      <c r="A17" s="15">
-        <v>46031</v>
-      </c>
-      <c r="B17" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="C17" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="D17" s="16">
-        <v>4695</v>
-      </c>
-      <c r="E17" s="16">
-        <v>0</v>
-      </c>
-      <c r="F17" s="16">
-        <v>46.95</v>
-      </c>
-      <c r="G17" s="16">
-        <v>0</v>
-      </c>
+      <c r="A17" s="15"/>
+      <c r="B17" s="12"/>
+      <c r="C17" s="12"/>
+      <c r="D17" s="16"/>
+      <c r="E17" s="16"/>
+      <c r="F17" s="16"/>
+      <c r="G17" s="16"/>
       <c r="H17" s="17"/>
       <c r="I17" s="4"/>
       <c r="J17" s="4"/>
@@ -1428,27 +898,13 @@
       <c r="Z17" s="4"/>
     </row>
     <row r="18" spans="1:26">
-      <c r="A18" s="15">
-        <v>46031</v>
-      </c>
-      <c r="B18" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="C18" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="D18" s="14">
-        <v>318</v>
-      </c>
-      <c r="E18" s="16">
-        <v>0</v>
-      </c>
-      <c r="F18" s="14">
-        <v>318</v>
-      </c>
-      <c r="G18" s="16">
-        <v>0</v>
-      </c>
+      <c r="A18" s="15"/>
+      <c r="B18" s="12"/>
+      <c r="C18" s="13"/>
+      <c r="D18" s="14"/>
+      <c r="E18" s="16"/>
+      <c r="F18" s="14"/>
+      <c r="G18" s="16"/>
       <c r="H18" s="17"/>
       <c r="I18" s="4"/>
       <c r="J18" s="4"/>
@@ -1470,27 +926,13 @@
       <c r="Z18" s="4"/>
     </row>
     <row r="19" spans="1:26">
-      <c r="A19" s="15">
-        <v>46035</v>
-      </c>
-      <c r="B19" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="C19" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="D19" s="16">
-        <v>101</v>
-      </c>
-      <c r="E19" s="16">
-        <v>0</v>
-      </c>
-      <c r="F19" s="16">
-        <v>101</v>
-      </c>
-      <c r="G19" s="16">
-        <v>0</v>
-      </c>
+      <c r="A19" s="15"/>
+      <c r="B19" s="12"/>
+      <c r="C19" s="12"/>
+      <c r="D19" s="16"/>
+      <c r="E19" s="16"/>
+      <c r="F19" s="16"/>
+      <c r="G19" s="16"/>
       <c r="H19" s="17"/>
       <c r="I19" s="4"/>
       <c r="J19" s="4"/>
@@ -1512,27 +954,13 @@
       <c r="Z19" s="4"/>
     </row>
     <row r="20" spans="1:26">
-      <c r="A20" s="15">
-        <v>46035</v>
-      </c>
-      <c r="B20" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="C20" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="D20" s="16">
-        <v>149.99</v>
-      </c>
-      <c r="E20" s="16">
-        <v>0</v>
-      </c>
-      <c r="F20" s="16">
-        <v>149.99</v>
-      </c>
-      <c r="G20" s="16">
-        <v>0</v>
-      </c>
+      <c r="A20" s="15"/>
+      <c r="B20" s="6"/>
+      <c r="C20" s="12"/>
+      <c r="D20" s="16"/>
+      <c r="E20" s="16"/>
+      <c r="F20" s="16"/>
+      <c r="G20" s="16"/>
       <c r="H20" s="17"/>
       <c r="I20" s="4"/>
       <c r="J20" s="4"/>
@@ -1554,27 +982,13 @@
       <c r="Z20" s="4"/>
     </row>
     <row r="21" spans="1:26">
-      <c r="A21" s="15">
-        <v>46035</v>
-      </c>
-      <c r="B21" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="C21" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="D21" s="16">
-        <v>159.03</v>
-      </c>
-      <c r="E21" s="16">
-        <v>7.98</v>
-      </c>
-      <c r="F21" s="16">
-        <v>167.01</v>
-      </c>
-      <c r="G21" s="16">
-        <v>0</v>
-      </c>
+      <c r="A21" s="15"/>
+      <c r="B21" s="12"/>
+      <c r="C21" s="12"/>
+      <c r="D21" s="16"/>
+      <c r="E21" s="16"/>
+      <c r="F21" s="16"/>
+      <c r="G21" s="16"/>
       <c r="H21" s="17"/>
       <c r="I21" s="4"/>
       <c r="J21" s="4"/>
@@ -1596,27 +1010,13 @@
       <c r="Z21" s="4"/>
     </row>
     <row r="22" spans="1:26">
-      <c r="A22" s="15">
-        <v>46036</v>
-      </c>
-      <c r="B22" s="12" t="s">
-        <v>42</v>
-      </c>
-      <c r="C22" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="D22" s="16">
-        <v>28.09</v>
-      </c>
-      <c r="E22" s="16">
-        <v>0</v>
-      </c>
-      <c r="F22" s="16">
-        <v>28.09</v>
-      </c>
-      <c r="G22" s="16">
-        <v>0</v>
-      </c>
+      <c r="A22" s="15"/>
+      <c r="B22" s="12"/>
+      <c r="C22" s="12"/>
+      <c r="D22" s="16"/>
+      <c r="E22" s="16"/>
+      <c r="F22" s="16"/>
+      <c r="G22" s="16"/>
       <c r="H22" s="17"/>
       <c r="I22" s="4"/>
       <c r="J22" s="4"/>
@@ -1638,27 +1038,13 @@
       <c r="Z22" s="4"/>
     </row>
     <row r="23" spans="1:26">
-      <c r="A23" s="15">
-        <v>46036</v>
-      </c>
-      <c r="B23" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="C23" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="D23" s="16">
-        <v>113.39</v>
-      </c>
-      <c r="E23" s="16">
-        <v>0</v>
-      </c>
-      <c r="F23" s="16">
-        <v>113.39</v>
-      </c>
-      <c r="G23" s="16">
-        <v>0</v>
-      </c>
+      <c r="A23" s="15"/>
+      <c r="B23" s="6"/>
+      <c r="C23" s="6"/>
+      <c r="D23" s="16"/>
+      <c r="E23" s="16"/>
+      <c r="F23" s="16"/>
+      <c r="G23" s="16"/>
       <c r="H23" s="17"/>
       <c r="I23" s="4"/>
       <c r="J23" s="4"/>
@@ -1680,27 +1066,13 @@
       <c r="Z23" s="4"/>
     </row>
     <row r="24" spans="1:26">
-      <c r="A24" s="15">
-        <v>46037</v>
-      </c>
-      <c r="B24" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="C24" s="12" t="s">
-        <v>44</v>
-      </c>
-      <c r="D24" s="16">
-        <v>9.99</v>
-      </c>
-      <c r="E24" s="16">
-        <v>1.5</v>
-      </c>
-      <c r="F24" s="16">
-        <v>11.49</v>
-      </c>
-      <c r="G24" s="16">
-        <v>0</v>
-      </c>
+      <c r="A24" s="15"/>
+      <c r="B24" s="12"/>
+      <c r="C24" s="12"/>
+      <c r="D24" s="16"/>
+      <c r="E24" s="16"/>
+      <c r="F24" s="16"/>
+      <c r="G24" s="16"/>
       <c r="H24" s="17"/>
       <c r="I24" s="4"/>
       <c r="J24" s="4"/>
@@ -1722,27 +1094,13 @@
       <c r="Z24" s="4"/>
     </row>
     <row r="25" spans="1:26">
-      <c r="A25" s="15">
-        <v>46039</v>
-      </c>
-      <c r="B25" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="C25" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="D25" s="16">
-        <v>10</v>
-      </c>
-      <c r="E25" s="16">
-        <v>0</v>
-      </c>
-      <c r="F25" s="16">
-        <v>10</v>
-      </c>
-      <c r="G25" s="16">
-        <v>0</v>
-      </c>
+      <c r="A25" s="15"/>
+      <c r="B25" s="12"/>
+      <c r="C25" s="12"/>
+      <c r="D25" s="16"/>
+      <c r="E25" s="16"/>
+      <c r="F25" s="16"/>
+      <c r="G25" s="16"/>
       <c r="H25" s="17"/>
       <c r="I25" s="4"/>
       <c r="J25" s="4"/>
@@ -1764,27 +1122,13 @@
       <c r="Z25" s="4"/>
     </row>
     <row r="26" spans="1:26">
-      <c r="A26" s="15">
-        <v>46039</v>
-      </c>
-      <c r="B26" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="C26" s="12" t="s">
-        <v>47</v>
-      </c>
-      <c r="D26" s="14">
-        <v>28.28</v>
-      </c>
-      <c r="E26" s="16">
-        <v>0</v>
-      </c>
-      <c r="F26" s="14">
-        <v>28.28</v>
-      </c>
-      <c r="G26" s="16">
-        <v>0</v>
-      </c>
+      <c r="A26" s="15"/>
+      <c r="B26" s="12"/>
+      <c r="C26" s="12"/>
+      <c r="D26" s="14"/>
+      <c r="E26" s="16"/>
+      <c r="F26" s="14"/>
+      <c r="G26" s="16"/>
       <c r="H26" s="17"/>
       <c r="I26" s="4"/>
       <c r="J26" s="4"/>
@@ -1806,27 +1150,13 @@
       <c r="Z26" s="4"/>
     </row>
     <row r="27" spans="1:26">
-      <c r="A27" s="15">
-        <v>46040</v>
-      </c>
-      <c r="B27" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="C27" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="D27" s="16">
-        <v>10.99</v>
-      </c>
-      <c r="E27" s="16">
-        <v>0</v>
-      </c>
-      <c r="F27" s="16">
-        <v>10.99</v>
-      </c>
-      <c r="G27" s="16">
-        <v>0</v>
-      </c>
+      <c r="A27" s="15"/>
+      <c r="B27" s="12"/>
+      <c r="C27" s="12"/>
+      <c r="D27" s="16"/>
+      <c r="E27" s="16"/>
+      <c r="F27" s="16"/>
+      <c r="G27" s="16"/>
       <c r="H27" s="17"/>
       <c r="I27" s="4"/>
       <c r="J27" s="4"/>
@@ -1848,27 +1178,13 @@
       <c r="Z27" s="4"/>
     </row>
     <row r="28" spans="1:26">
-      <c r="A28" s="15">
-        <v>46042</v>
-      </c>
-      <c r="B28" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="C28" s="12" t="s">
-        <v>50</v>
-      </c>
-      <c r="D28" s="16">
-        <v>93</v>
-      </c>
-      <c r="E28" s="16">
-        <v>0</v>
-      </c>
-      <c r="F28" s="16">
-        <v>93</v>
-      </c>
-      <c r="G28" s="16">
-        <v>0</v>
-      </c>
+      <c r="A28" s="15"/>
+      <c r="B28" s="12"/>
+      <c r="C28" s="12"/>
+      <c r="D28" s="16"/>
+      <c r="E28" s="16"/>
+      <c r="F28" s="16"/>
+      <c r="G28" s="16"/>
       <c r="H28" s="17"/>
       <c r="I28" s="4"/>
       <c r="J28" s="4"/>
@@ -1890,27 +1206,13 @@
       <c r="Z28" s="4"/>
     </row>
     <row r="29" spans="1:26">
-      <c r="A29" s="15">
-        <v>46042</v>
-      </c>
-      <c r="B29" s="12" t="s">
-        <v>51</v>
-      </c>
-      <c r="C29" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="D29" s="16">
-        <v>101.55</v>
-      </c>
-      <c r="E29" s="16">
-        <v>0</v>
-      </c>
-      <c r="F29" s="16">
-        <v>101.55</v>
-      </c>
-      <c r="G29" s="16">
-        <v>0</v>
-      </c>
+      <c r="A29" s="15"/>
+      <c r="B29" s="12"/>
+      <c r="C29" s="12"/>
+      <c r="D29" s="16"/>
+      <c r="E29" s="16"/>
+      <c r="F29" s="16"/>
+      <c r="G29" s="16"/>
       <c r="H29" s="17"/>
       <c r="I29" s="4"/>
       <c r="J29" s="4"/>
@@ -1932,27 +1234,13 @@
       <c r="Z29" s="4"/>
     </row>
     <row r="30" spans="1:26">
-      <c r="A30" s="15">
-        <v>46043</v>
-      </c>
-      <c r="B30" s="12" t="s">
-        <v>53</v>
-      </c>
-      <c r="C30" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="D30" s="16">
-        <v>34.28</v>
-      </c>
-      <c r="E30" s="16">
-        <v>0</v>
-      </c>
-      <c r="F30" s="16">
-        <v>34.28</v>
-      </c>
-      <c r="G30" s="16">
-        <v>0</v>
-      </c>
+      <c r="A30" s="15"/>
+      <c r="B30" s="12"/>
+      <c r="C30" s="9"/>
+      <c r="D30" s="16"/>
+      <c r="E30" s="16"/>
+      <c r="F30" s="16"/>
+      <c r="G30" s="16"/>
       <c r="H30" s="17"/>
       <c r="I30" s="4"/>
       <c r="J30" s="4"/>
@@ -1974,27 +1262,13 @@
       <c r="Z30" s="4"/>
     </row>
     <row r="31" spans="1:26">
-      <c r="A31" s="15">
-        <v>46043</v>
-      </c>
-      <c r="B31" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="C31" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="D31" s="16">
-        <v>137.44999999999999</v>
-      </c>
-      <c r="E31" s="16">
-        <v>7.51</v>
-      </c>
-      <c r="F31" s="16">
-        <v>144.96</v>
-      </c>
-      <c r="G31" s="16">
-        <v>0</v>
-      </c>
+      <c r="A31" s="15"/>
+      <c r="B31" s="12"/>
+      <c r="C31" s="12"/>
+      <c r="D31" s="16"/>
+      <c r="E31" s="16"/>
+      <c r="F31" s="16"/>
+      <c r="G31" s="16"/>
       <c r="H31" s="17"/>
       <c r="I31" s="4"/>
       <c r="J31" s="4"/>
@@ -2016,27 +1290,13 @@
       <c r="Z31" s="4"/>
     </row>
     <row r="32" spans="1:26">
-      <c r="A32" s="15">
-        <v>46043</v>
-      </c>
-      <c r="B32" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="C32" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="D32" s="16">
-        <v>11.98</v>
-      </c>
-      <c r="E32" s="16">
-        <v>0</v>
-      </c>
-      <c r="F32" s="16">
-        <v>11.98</v>
-      </c>
-      <c r="G32" s="16">
-        <v>0</v>
-      </c>
+      <c r="A32" s="15"/>
+      <c r="B32" s="12"/>
+      <c r="C32" s="12"/>
+      <c r="D32" s="16"/>
+      <c r="E32" s="16"/>
+      <c r="F32" s="16"/>
+      <c r="G32" s="16"/>
       <c r="H32" s="17"/>
       <c r="I32" s="4"/>
       <c r="J32" s="4"/>
@@ -2058,27 +1318,13 @@
       <c r="Z32" s="4"/>
     </row>
     <row r="33" spans="1:26">
-      <c r="A33" s="15">
-        <v>46044</v>
-      </c>
-      <c r="B33" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="C33" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="D33" s="14">
-        <v>48.49</v>
-      </c>
-      <c r="E33" s="16">
-        <v>0</v>
-      </c>
-      <c r="F33" s="14">
-        <v>48.49</v>
-      </c>
-      <c r="G33" s="16">
-        <v>0</v>
-      </c>
+      <c r="A33" s="15"/>
+      <c r="B33" s="12"/>
+      <c r="C33" s="12"/>
+      <c r="D33" s="14"/>
+      <c r="E33" s="16"/>
+      <c r="F33" s="14"/>
+      <c r="G33" s="16"/>
       <c r="H33" s="17"/>
       <c r="I33" s="4"/>
       <c r="J33" s="4"/>
@@ -2100,27 +1346,13 @@
       <c r="Z33" s="4"/>
     </row>
     <row r="34" spans="1:26">
-      <c r="A34" s="15">
-        <v>46045</v>
-      </c>
-      <c r="B34" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="C34" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="D34" s="16">
-        <v>12.99</v>
-      </c>
-      <c r="E34" s="16">
-        <v>0</v>
-      </c>
-      <c r="F34" s="16">
-        <v>12.99</v>
-      </c>
-      <c r="G34" s="16">
-        <v>0</v>
-      </c>
+      <c r="A34" s="15"/>
+      <c r="B34" s="12"/>
+      <c r="C34" s="12"/>
+      <c r="D34" s="16"/>
+      <c r="E34" s="16"/>
+      <c r="F34" s="16"/>
+      <c r="G34" s="16"/>
       <c r="H34" s="17"/>
       <c r="I34" s="4"/>
       <c r="J34" s="4"/>
@@ -2142,27 +1374,13 @@
       <c r="Z34" s="4"/>
     </row>
     <row r="35" spans="1:26">
-      <c r="A35" s="15">
-        <v>46045</v>
-      </c>
-      <c r="B35" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="C35" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="D35" s="16">
-        <v>93.89</v>
-      </c>
-      <c r="E35" s="16">
-        <v>4.47</v>
-      </c>
-      <c r="F35" s="16">
-        <v>98.36</v>
-      </c>
-      <c r="G35" s="16">
-        <v>0</v>
-      </c>
+      <c r="A35" s="15"/>
+      <c r="B35" s="12"/>
+      <c r="C35" s="12"/>
+      <c r="D35" s="16"/>
+      <c r="E35" s="16"/>
+      <c r="F35" s="16"/>
+      <c r="G35" s="16"/>
       <c r="H35" s="17"/>
       <c r="I35" s="4"/>
       <c r="J35" s="4"/>
@@ -2184,27 +1402,13 @@
       <c r="Z35" s="4"/>
     </row>
     <row r="36" spans="1:26">
-      <c r="A36" s="15">
-        <v>46046</v>
-      </c>
-      <c r="B36" s="12" t="s">
-        <v>56</v>
-      </c>
-      <c r="C36" s="12" t="s">
-        <v>57</v>
-      </c>
-      <c r="D36" s="16">
-        <v>1086</v>
-      </c>
-      <c r="E36" s="16">
-        <v>0</v>
-      </c>
-      <c r="F36" s="16">
-        <v>1086</v>
-      </c>
-      <c r="G36" s="16">
-        <v>0</v>
-      </c>
+      <c r="A36" s="15"/>
+      <c r="B36" s="12"/>
+      <c r="C36" s="12"/>
+      <c r="D36" s="16"/>
+      <c r="E36" s="16"/>
+      <c r="F36" s="16"/>
+      <c r="G36" s="16"/>
       <c r="H36" s="17"/>
       <c r="I36" s="4"/>
       <c r="J36" s="4"/>
@@ -2226,27 +1430,13 @@
       <c r="Z36" s="4"/>
     </row>
     <row r="37" spans="1:26">
-      <c r="A37" s="15">
-        <v>46048</v>
-      </c>
-      <c r="B37" s="12" t="s">
-        <v>56</v>
-      </c>
-      <c r="C37" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="D37" s="14">
-        <v>1153</v>
-      </c>
-      <c r="E37" s="16">
-        <v>0</v>
-      </c>
-      <c r="F37" s="14">
-        <v>1153</v>
-      </c>
-      <c r="G37" s="16">
-        <v>0</v>
-      </c>
+      <c r="A37" s="15"/>
+      <c r="B37" s="12"/>
+      <c r="C37" s="12"/>
+      <c r="D37" s="14"/>
+      <c r="E37" s="16"/>
+      <c r="F37" s="14"/>
+      <c r="G37" s="16"/>
       <c r="H37" s="17"/>
       <c r="I37" s="4"/>
       <c r="J37" s="4"/>
@@ -2268,27 +1458,13 @@
       <c r="Z37" s="4"/>
     </row>
     <row r="38" spans="1:26">
-      <c r="A38" s="15">
-        <v>46050</v>
-      </c>
-      <c r="B38" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="C38" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="D38" s="16">
-        <v>195.47</v>
-      </c>
-      <c r="E38" s="16">
-        <v>0</v>
-      </c>
-      <c r="F38" s="16">
-        <v>195.47</v>
-      </c>
-      <c r="G38" s="16">
-        <v>0</v>
-      </c>
+      <c r="A38" s="15"/>
+      <c r="B38" s="12"/>
+      <c r="C38" s="12"/>
+      <c r="D38" s="16"/>
+      <c r="E38" s="16"/>
+      <c r="F38" s="16"/>
+      <c r="G38" s="16"/>
       <c r="H38" s="17"/>
       <c r="I38" s="4"/>
       <c r="J38" s="4"/>
@@ -2310,27 +1486,13 @@
       <c r="Z38" s="4"/>
     </row>
     <row r="39" spans="1:26">
-      <c r="A39" s="15">
-        <v>46050</v>
-      </c>
-      <c r="B39" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C39" s="12" t="s">
-        <v>59</v>
-      </c>
-      <c r="D39" s="16">
-        <v>129.99</v>
-      </c>
-      <c r="E39" s="16">
-        <v>9.1</v>
-      </c>
-      <c r="F39" s="16">
-        <v>139.09</v>
-      </c>
-      <c r="G39" s="16">
-        <v>0</v>
-      </c>
+      <c r="A39" s="15"/>
+      <c r="B39" s="6"/>
+      <c r="C39" s="12"/>
+      <c r="D39" s="16"/>
+      <c r="E39" s="16"/>
+      <c r="F39" s="16"/>
+      <c r="G39" s="16"/>
       <c r="H39" s="17"/>
       <c r="I39" s="4"/>
       <c r="J39" s="4"/>
@@ -2352,27 +1514,13 @@
       <c r="Z39" s="4"/>
     </row>
     <row r="40" spans="1:26">
-      <c r="A40" s="15">
-        <v>46050</v>
-      </c>
-      <c r="B40" s="12" t="s">
-        <v>60</v>
-      </c>
-      <c r="C40" s="12" t="s">
-        <v>61</v>
-      </c>
-      <c r="D40" s="16">
-        <v>21.21</v>
-      </c>
-      <c r="E40" s="16">
-        <v>0</v>
-      </c>
-      <c r="F40" s="16">
-        <v>21.21</v>
-      </c>
-      <c r="G40" s="16">
-        <v>0</v>
-      </c>
+      <c r="A40" s="15"/>
+      <c r="B40" s="12"/>
+      <c r="C40" s="12"/>
+      <c r="D40" s="16"/>
+      <c r="E40" s="16"/>
+      <c r="F40" s="16"/>
+      <c r="G40" s="16"/>
       <c r="H40" s="17"/>
       <c r="I40" s="4"/>
       <c r="J40" s="4"/>
@@ -2394,27 +1542,13 @@
       <c r="Z40" s="4"/>
     </row>
     <row r="41" spans="1:26">
-      <c r="A41" s="15">
-        <v>46050</v>
-      </c>
-      <c r="B41" s="12" t="s">
-        <v>62</v>
-      </c>
-      <c r="C41" s="12" t="s">
-        <v>62</v>
-      </c>
-      <c r="D41" s="16">
-        <v>7.99</v>
-      </c>
-      <c r="E41" s="16">
-        <v>0</v>
-      </c>
-      <c r="F41" s="16">
-        <v>7.99</v>
-      </c>
-      <c r="G41" s="16">
-        <v>0</v>
-      </c>
+      <c r="A41" s="15"/>
+      <c r="B41" s="12"/>
+      <c r="C41" s="12"/>
+      <c r="D41" s="16"/>
+      <c r="E41" s="16"/>
+      <c r="F41" s="16"/>
+      <c r="G41" s="16"/>
       <c r="H41" s="17"/>
       <c r="I41" s="4"/>
       <c r="J41" s="4"/>
@@ -2436,27 +1570,13 @@
       <c r="Z41" s="4"/>
     </row>
     <row r="42" spans="1:26">
-      <c r="A42" s="5">
-        <v>46050</v>
-      </c>
-      <c r="B42" s="12" t="s">
-        <v>63</v>
-      </c>
-      <c r="C42" s="12" t="s">
-        <v>61</v>
-      </c>
-      <c r="D42" s="14">
-        <v>382.8</v>
-      </c>
-      <c r="E42" s="16">
-        <v>0</v>
-      </c>
-      <c r="F42" s="14">
-        <v>382.8</v>
-      </c>
-      <c r="G42" s="16">
-        <v>0</v>
-      </c>
+      <c r="A42" s="5"/>
+      <c r="B42" s="12"/>
+      <c r="C42" s="12"/>
+      <c r="D42" s="14"/>
+      <c r="E42" s="16"/>
+      <c r="F42" s="14"/>
+      <c r="G42" s="16"/>
       <c r="H42" s="6"/>
       <c r="I42" s="4"/>
       <c r="J42" s="4"/>
@@ -2478,27 +1598,13 @@
       <c r="Z42" s="4"/>
     </row>
     <row r="43" spans="1:26">
-      <c r="A43" s="5">
-        <v>46051</v>
-      </c>
-      <c r="B43" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="C43" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="D43" s="7">
-        <v>99</v>
-      </c>
-      <c r="E43" s="7">
-        <v>0</v>
-      </c>
-      <c r="F43" s="7">
-        <v>99</v>
-      </c>
-      <c r="G43" s="7">
-        <v>0</v>
-      </c>
+      <c r="A43" s="5"/>
+      <c r="B43" s="6"/>
+      <c r="C43" s="6"/>
+      <c r="D43" s="7"/>
+      <c r="E43" s="7"/>
+      <c r="F43" s="7"/>
+      <c r="G43" s="7"/>
       <c r="H43" s="6"/>
       <c r="I43" s="4"/>
       <c r="J43" s="4"/>
@@ -2520,27 +1626,13 @@
       <c r="Z43" s="4"/>
     </row>
     <row r="44" spans="1:26">
-      <c r="A44" s="11">
-        <v>46052</v>
-      </c>
-      <c r="B44" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C44" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="D44" s="7">
-        <v>32.869999999999997</v>
-      </c>
-      <c r="E44" s="7">
-        <v>2.4700000000000002</v>
-      </c>
-      <c r="F44" s="7">
-        <v>35.340000000000003</v>
-      </c>
-      <c r="G44" s="7">
-        <v>0</v>
-      </c>
+      <c r="A44" s="11"/>
+      <c r="B44" s="6"/>
+      <c r="C44" s="6"/>
+      <c r="D44" s="7"/>
+      <c r="E44" s="7"/>
+      <c r="F44" s="7"/>
+      <c r="G44" s="7"/>
       <c r="H44" s="6"/>
       <c r="I44" s="4"/>
       <c r="J44" s="4"/>
@@ -2562,27 +1654,13 @@
       <c r="Z44" s="4"/>
     </row>
     <row r="45" spans="1:26">
-      <c r="A45" s="18">
-        <v>46053</v>
-      </c>
-      <c r="B45" s="12" t="s">
-        <v>51</v>
-      </c>
-      <c r="C45" s="12" t="s">
-        <v>65</v>
-      </c>
-      <c r="D45" s="16">
-        <v>85.33</v>
-      </c>
-      <c r="E45" s="16">
-        <v>0</v>
-      </c>
-      <c r="F45" s="16">
-        <v>85.33</v>
-      </c>
-      <c r="G45" s="16">
-        <v>0</v>
-      </c>
+      <c r="A45" s="18"/>
+      <c r="B45" s="12"/>
+      <c r="C45" s="12"/>
+      <c r="D45" s="16"/>
+      <c r="E45" s="16"/>
+      <c r="F45" s="16"/>
+      <c r="G45" s="16"/>
       <c r="H45" s="17"/>
       <c r="I45" s="4"/>
       <c r="J45" s="4"/>
@@ -2604,27 +1682,13 @@
       <c r="Z45" s="4"/>
     </row>
     <row r="46" spans="1:26">
-      <c r="A46" s="15">
-        <v>46053</v>
-      </c>
-      <c r="B46" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="C46" s="12" t="s">
-        <v>67</v>
-      </c>
-      <c r="D46" s="16">
-        <v>741.41</v>
-      </c>
-      <c r="E46" s="16">
-        <v>92.68</v>
-      </c>
-      <c r="F46" s="16">
-        <v>834.09</v>
-      </c>
-      <c r="G46" s="16">
-        <v>0</v>
-      </c>
+      <c r="A46" s="15"/>
+      <c r="B46" s="6"/>
+      <c r="C46" s="12"/>
+      <c r="D46" s="16"/>
+      <c r="E46" s="16"/>
+      <c r="F46" s="16"/>
+      <c r="G46" s="16"/>
       <c r="H46" s="17"/>
       <c r="I46" s="4"/>
       <c r="J46" s="4"/>
@@ -2646,27 +1710,13 @@
       <c r="Z46" s="4"/>
     </row>
     <row r="47" spans="1:26">
-      <c r="A47" s="15">
-        <v>46053</v>
-      </c>
-      <c r="B47" s="12" t="s">
-        <v>42</v>
-      </c>
-      <c r="C47" s="12" t="s">
-        <v>68</v>
-      </c>
-      <c r="D47" s="16">
-        <v>37</v>
-      </c>
-      <c r="E47" s="16">
-        <v>0</v>
-      </c>
-      <c r="F47" s="16">
-        <v>37</v>
-      </c>
-      <c r="G47" s="16">
-        <v>0</v>
-      </c>
+      <c r="A47" s="15"/>
+      <c r="B47" s="12"/>
+      <c r="C47" s="12"/>
+      <c r="D47" s="16"/>
+      <c r="E47" s="16"/>
+      <c r="F47" s="16"/>
+      <c r="G47" s="16"/>
       <c r="H47" s="17"/>
       <c r="I47" s="4"/>
       <c r="J47" s="4"/>
@@ -2688,27 +1738,13 @@
       <c r="Z47" s="4"/>
     </row>
     <row r="48" spans="1:26">
-      <c r="A48" s="11">
-        <v>46055</v>
-      </c>
-      <c r="B48" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="C48" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="D48" s="10">
-        <v>886.7</v>
-      </c>
-      <c r="E48" s="7">
-        <v>0</v>
-      </c>
-      <c r="F48" s="10">
-        <v>886.7</v>
-      </c>
-      <c r="G48" s="7">
-        <v>0</v>
-      </c>
+      <c r="A48" s="11"/>
+      <c r="B48" s="6"/>
+      <c r="C48" s="6"/>
+      <c r="D48" s="10"/>
+      <c r="E48" s="7"/>
+      <c r="F48" s="10"/>
+      <c r="G48" s="7"/>
       <c r="H48" s="6"/>
       <c r="I48" s="12"/>
       <c r="J48" s="4"/>
@@ -2730,27 +1766,13 @@
       <c r="Z48" s="4"/>
     </row>
     <row r="49" spans="1:26">
-      <c r="A49" s="11">
-        <v>46055</v>
-      </c>
-      <c r="B49" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="C49" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="D49" s="14">
-        <v>28.29</v>
-      </c>
-      <c r="E49" s="7">
-        <v>0</v>
-      </c>
-      <c r="F49" s="14">
-        <v>28.29</v>
-      </c>
-      <c r="G49" s="7">
-        <v>0</v>
-      </c>
+      <c r="A49" s="11"/>
+      <c r="B49" s="12"/>
+      <c r="C49" s="13"/>
+      <c r="D49" s="14"/>
+      <c r="E49" s="7"/>
+      <c r="F49" s="14"/>
+      <c r="G49" s="7"/>
       <c r="H49" s="6"/>
       <c r="I49" s="4"/>
       <c r="J49" s="4"/>
@@ -2772,27 +1794,13 @@
       <c r="Z49" s="4"/>
     </row>
     <row r="50" spans="1:26">
-      <c r="A50" s="11">
-        <v>46058</v>
-      </c>
-      <c r="B50" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="C50" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="D50" s="14">
-        <v>36</v>
-      </c>
-      <c r="E50" s="7">
-        <v>0</v>
-      </c>
-      <c r="F50" s="14">
-        <v>36</v>
-      </c>
-      <c r="G50" s="7">
-        <v>0</v>
-      </c>
+      <c r="A50" s="11"/>
+      <c r="B50" s="6"/>
+      <c r="C50" s="6"/>
+      <c r="D50" s="14"/>
+      <c r="E50" s="7"/>
+      <c r="F50" s="14"/>
+      <c r="G50" s="7"/>
       <c r="H50" s="6"/>
       <c r="I50" s="4"/>
       <c r="J50" s="4"/>
@@ -2814,27 +1822,13 @@
       <c r="Z50" s="4"/>
     </row>
     <row r="51" spans="1:26">
-      <c r="A51" s="15">
-        <v>46060</v>
-      </c>
-      <c r="B51" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="C51" s="12" t="s">
-        <v>69</v>
-      </c>
-      <c r="D51" s="16">
-        <v>551</v>
-      </c>
-      <c r="E51" s="16">
-        <v>82.38</v>
-      </c>
-      <c r="F51" s="16">
-        <v>633.38</v>
-      </c>
-      <c r="G51" s="16">
-        <v>0</v>
-      </c>
+      <c r="A51" s="15"/>
+      <c r="B51" s="6"/>
+      <c r="C51" s="12"/>
+      <c r="D51" s="16"/>
+      <c r="E51" s="16"/>
+      <c r="F51" s="16"/>
+      <c r="G51" s="16"/>
       <c r="H51" s="17"/>
       <c r="I51" s="4"/>
       <c r="J51" s="4"/>
@@ -2856,27 +1850,13 @@
       <c r="Z51" s="4"/>
     </row>
     <row r="52" spans="1:26">
-      <c r="A52" s="15">
-        <v>46060</v>
-      </c>
-      <c r="B52" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="C52" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="D52" s="14">
-        <v>318</v>
-      </c>
-      <c r="E52" s="16">
-        <v>0</v>
-      </c>
-      <c r="F52" s="14">
-        <v>318</v>
-      </c>
-      <c r="G52" s="16">
-        <v>0</v>
-      </c>
+      <c r="A52" s="15"/>
+      <c r="B52" s="12"/>
+      <c r="C52" s="13"/>
+      <c r="D52" s="14"/>
+      <c r="E52" s="16"/>
+      <c r="F52" s="14"/>
+      <c r="G52" s="16"/>
       <c r="H52" s="17"/>
       <c r="I52" s="4"/>
       <c r="J52" s="4"/>
@@ -2898,27 +1878,13 @@
       <c r="Z52" s="4"/>
     </row>
     <row r="53" spans="1:26">
-      <c r="A53" s="15">
-        <v>46061</v>
-      </c>
-      <c r="B53" s="12" t="s">
-        <v>70</v>
-      </c>
-      <c r="C53" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="D53" s="14">
-        <v>39.799999999999997</v>
-      </c>
-      <c r="E53" s="16">
-        <v>0</v>
-      </c>
-      <c r="F53" s="14">
-        <v>39.799999999999997</v>
-      </c>
-      <c r="G53" s="16">
-        <v>0</v>
-      </c>
+      <c r="A53" s="15"/>
+      <c r="B53" s="12"/>
+      <c r="C53" s="12"/>
+      <c r="D53" s="14"/>
+      <c r="E53" s="16"/>
+      <c r="F53" s="14"/>
+      <c r="G53" s="16"/>
       <c r="H53" s="17"/>
       <c r="I53" s="4"/>
       <c r="J53" s="4"/>
@@ -2940,27 +1906,13 @@
       <c r="Z53" s="4"/>
     </row>
     <row r="54" spans="1:26">
-      <c r="A54" s="15">
-        <v>46065</v>
-      </c>
-      <c r="B54" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="C54" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="D54" s="16">
-        <v>101</v>
-      </c>
-      <c r="E54" s="16">
-        <v>0</v>
-      </c>
-      <c r="F54" s="16">
-        <v>101</v>
-      </c>
-      <c r="G54" s="16">
-        <v>0</v>
-      </c>
+      <c r="A54" s="15"/>
+      <c r="B54" s="12"/>
+      <c r="C54" s="12"/>
+      <c r="D54" s="16"/>
+      <c r="E54" s="16"/>
+      <c r="F54" s="16"/>
+      <c r="G54" s="16"/>
       <c r="H54" s="17"/>
       <c r="I54" s="4"/>
       <c r="J54" s="4"/>
@@ -2982,27 +1934,13 @@
       <c r="Z54" s="4"/>
     </row>
     <row r="55" spans="1:26">
-      <c r="A55" s="5">
-        <v>46066</v>
-      </c>
-      <c r="B55" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C55" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="D55" s="7">
-        <v>1.39</v>
-      </c>
-      <c r="E55" s="7">
-        <v>0.1</v>
-      </c>
-      <c r="F55" s="7">
-        <v>1.49</v>
-      </c>
-      <c r="G55" s="7">
-        <v>0</v>
-      </c>
+      <c r="A55" s="5"/>
+      <c r="B55" s="6"/>
+      <c r="C55" s="6"/>
+      <c r="D55" s="7"/>
+      <c r="E55" s="7"/>
+      <c r="F55" s="7"/>
+      <c r="G55" s="7"/>
       <c r="H55" s="6"/>
       <c r="I55" s="4"/>
       <c r="J55" s="4"/>
@@ -3024,96 +1962,40 @@
       <c r="Z55" s="4"/>
     </row>
     <row r="56" spans="1:26">
-      <c r="A56" s="15">
-        <v>46068</v>
-      </c>
-      <c r="B56" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="C56" s="12" t="s">
-        <v>72</v>
-      </c>
-      <c r="D56" s="16">
-        <v>472.43</v>
-      </c>
-      <c r="E56" s="16">
-        <v>71.680000000000007</v>
-      </c>
-      <c r="F56" s="16">
-        <v>544.11</v>
-      </c>
-      <c r="G56" s="16">
-        <v>0</v>
-      </c>
+      <c r="A56" s="15"/>
+      <c r="B56" s="6"/>
+      <c r="C56" s="12"/>
+      <c r="D56" s="16"/>
+      <c r="E56" s="16"/>
+      <c r="F56" s="16"/>
+      <c r="G56" s="16"/>
     </row>
     <row r="57" spans="1:26">
-      <c r="A57" s="19">
-        <v>46068</v>
-      </c>
-      <c r="B57" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C57" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="D57" s="10">
-        <v>22.46</v>
-      </c>
-      <c r="E57" s="10">
-        <v>1.57</v>
-      </c>
-      <c r="F57" s="10">
-        <v>24.03</v>
-      </c>
-      <c r="G57" s="10">
-        <v>0</v>
-      </c>
+      <c r="A57" s="19"/>
+      <c r="B57" s="6"/>
+      <c r="C57" s="6"/>
+      <c r="D57" s="10"/>
+      <c r="E57" s="10"/>
+      <c r="F57" s="10"/>
+      <c r="G57" s="10"/>
     </row>
     <row r="58" spans="1:26">
-      <c r="A58" s="19">
-        <v>46071</v>
-      </c>
-      <c r="B58" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C58" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="D58" s="10">
-        <v>51.91</v>
-      </c>
-      <c r="E58" s="10">
-        <v>0.38</v>
-      </c>
-      <c r="F58" s="10">
-        <v>52.29</v>
-      </c>
-      <c r="G58" s="10">
-        <v>0</v>
-      </c>
+      <c r="A58" s="19"/>
+      <c r="B58" s="6"/>
+      <c r="C58" s="6"/>
+      <c r="D58" s="10"/>
+      <c r="E58" s="10"/>
+      <c r="F58" s="10"/>
+      <c r="G58" s="10"/>
     </row>
     <row r="59" spans="1:26">
-      <c r="A59" s="18">
-        <v>46072</v>
-      </c>
-      <c r="B59" s="12" t="s">
-        <v>51</v>
-      </c>
-      <c r="C59" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="D59" s="14">
-        <v>91.4</v>
-      </c>
-      <c r="E59" s="16">
-        <v>0</v>
-      </c>
-      <c r="F59" s="14">
-        <v>91.4</v>
-      </c>
-      <c r="G59" s="16">
-        <v>0</v>
-      </c>
+      <c r="A59" s="18"/>
+      <c r="B59" s="12"/>
+      <c r="C59" s="12"/>
+      <c r="D59" s="14"/>
+      <c r="E59" s="16"/>
+      <c r="F59" s="14"/>
+      <c r="G59" s="16"/>
       <c r="H59" s="17"/>
       <c r="I59" s="4"/>
       <c r="J59" s="4"/>
@@ -3135,119 +2017,49 @@
       <c r="Z59" s="4"/>
     </row>
     <row r="60" spans="1:26">
-      <c r="A60" s="19">
-        <v>46074</v>
-      </c>
-      <c r="B60" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C60" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="D60" s="10">
-        <v>149.56</v>
-      </c>
-      <c r="E60" s="10">
-        <v>1.47</v>
-      </c>
-      <c r="F60" s="10">
-        <v>151.03</v>
-      </c>
-      <c r="G60" s="10">
-        <v>0</v>
-      </c>
+      <c r="A60" s="19"/>
+      <c r="B60" s="6"/>
+      <c r="C60" s="6"/>
+      <c r="D60" s="10"/>
+      <c r="E60" s="10"/>
+      <c r="F60" s="10"/>
+      <c r="G60" s="10"/>
     </row>
     <row r="61" spans="1:26">
-      <c r="A61" s="19">
-        <v>46074</v>
-      </c>
-      <c r="B61" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C61" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="D61" s="10">
-        <v>20.77</v>
-      </c>
-      <c r="E61" s="10">
-        <v>0.8</v>
-      </c>
-      <c r="F61" s="10">
-        <v>21.57</v>
-      </c>
-      <c r="G61" s="10">
-        <v>0</v>
-      </c>
+      <c r="A61" s="19"/>
+      <c r="B61" s="6"/>
+      <c r="C61" s="6"/>
+      <c r="D61" s="10"/>
+      <c r="E61" s="10"/>
+      <c r="F61" s="10"/>
+      <c r="G61" s="10"/>
     </row>
     <row r="62" spans="1:26">
-      <c r="A62" s="19">
-        <v>46074</v>
-      </c>
-      <c r="B62" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C62" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="D62" s="10">
-        <v>25.07</v>
-      </c>
-      <c r="E62" s="10">
-        <v>1.75</v>
-      </c>
-      <c r="F62" s="10">
-        <v>30.69</v>
-      </c>
-      <c r="G62" s="10">
-        <v>3.67</v>
-      </c>
+      <c r="A62" s="19"/>
+      <c r="B62" s="6"/>
+      <c r="C62" s="6"/>
+      <c r="D62" s="10"/>
+      <c r="E62" s="10"/>
+      <c r="F62" s="10"/>
+      <c r="G62" s="10"/>
     </row>
     <row r="63" spans="1:26">
-      <c r="A63" s="19">
-        <v>46074</v>
-      </c>
-      <c r="B63" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C63" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="D63" s="10">
-        <v>0</v>
-      </c>
-      <c r="E63" s="10">
-        <v>3.67</v>
-      </c>
-      <c r="F63" s="10">
-        <v>30.69</v>
-      </c>
-      <c r="G63" s="10">
-        <v>0</v>
-      </c>
+      <c r="A63" s="19"/>
+      <c r="B63" s="6"/>
+      <c r="C63" s="6"/>
+      <c r="D63" s="10"/>
+      <c r="E63" s="10"/>
+      <c r="F63" s="10"/>
+      <c r="G63" s="10"/>
     </row>
     <row r="64" spans="1:26">
-      <c r="A64" s="15">
-        <v>46074</v>
-      </c>
-      <c r="B64" s="12" t="s">
-        <v>56</v>
-      </c>
-      <c r="C64" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="D64" s="20">
-        <v>1000</v>
-      </c>
-      <c r="E64" s="16">
-        <v>0</v>
-      </c>
-      <c r="F64" s="20">
-        <v>1000</v>
-      </c>
-      <c r="G64" s="16">
-        <v>0</v>
-      </c>
+      <c r="A64" s="15"/>
+      <c r="B64" s="12"/>
+      <c r="C64" s="12"/>
+      <c r="D64" s="20"/>
+      <c r="E64" s="16"/>
+      <c r="F64" s="20"/>
+      <c r="G64" s="16"/>
       <c r="H64" s="17"/>
       <c r="I64" s="4"/>
       <c r="J64" s="4"/>
@@ -3269,27 +2081,13 @@
       <c r="Z64" s="4"/>
     </row>
     <row r="65" spans="1:26">
-      <c r="A65" s="18">
-        <v>46074</v>
-      </c>
-      <c r="B65" s="12" t="s">
-        <v>51</v>
-      </c>
-      <c r="C65" s="12" t="s">
-        <v>65</v>
-      </c>
-      <c r="D65" s="16">
-        <v>85.33</v>
-      </c>
-      <c r="E65" s="16">
-        <v>0</v>
-      </c>
-      <c r="F65" s="16">
-        <v>85.33</v>
-      </c>
-      <c r="G65" s="16">
-        <v>0</v>
-      </c>
+      <c r="A65" s="18"/>
+      <c r="B65" s="12"/>
+      <c r="C65" s="12"/>
+      <c r="D65" s="16"/>
+      <c r="E65" s="16"/>
+      <c r="F65" s="16"/>
+      <c r="G65" s="16"/>
       <c r="H65" s="17"/>
       <c r="I65" s="4"/>
       <c r="J65" s="4"/>
@@ -3311,27 +2109,13 @@
       <c r="Z65" s="4"/>
     </row>
     <row r="66" spans="1:26">
-      <c r="A66" s="15">
-        <v>46074</v>
-      </c>
-      <c r="B66" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="C66" s="12" t="s">
-        <v>50</v>
-      </c>
-      <c r="D66" s="16">
-        <v>93</v>
-      </c>
-      <c r="E66" s="16">
-        <v>0</v>
-      </c>
-      <c r="F66" s="16">
-        <v>93</v>
-      </c>
-      <c r="G66" s="16">
-        <v>0</v>
-      </c>
+      <c r="A66" s="15"/>
+      <c r="B66" s="12"/>
+      <c r="C66" s="12"/>
+      <c r="D66" s="16"/>
+      <c r="E66" s="16"/>
+      <c r="F66" s="16"/>
+      <c r="G66" s="16"/>
       <c r="H66" s="17"/>
       <c r="I66" s="4"/>
       <c r="J66" s="4"/>
@@ -3353,50 +2137,22 @@
       <c r="Z66" s="4"/>
     </row>
     <row r="67" spans="1:26">
-      <c r="A67" s="15">
-        <v>46075</v>
-      </c>
-      <c r="B67" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="C67" s="12" t="s">
-        <v>72</v>
-      </c>
-      <c r="D67" s="16">
-        <v>428.33</v>
-      </c>
-      <c r="E67" s="16">
-        <v>66.430000000000007</v>
-      </c>
-      <c r="F67" s="16">
-        <v>494.76</v>
-      </c>
-      <c r="G67" s="16">
-        <v>0</v>
-      </c>
+      <c r="A67" s="15"/>
+      <c r="B67" s="6"/>
+      <c r="C67" s="12"/>
+      <c r="D67" s="16"/>
+      <c r="E67" s="16"/>
+      <c r="F67" s="16"/>
+      <c r="G67" s="16"/>
     </row>
     <row r="68" spans="1:26">
-      <c r="A68" s="15">
-        <v>46077</v>
-      </c>
-      <c r="B68" s="12" t="s">
-        <v>56</v>
-      </c>
-      <c r="C68" s="12" t="s">
-        <v>57</v>
-      </c>
-      <c r="D68" s="10">
-        <v>1081.52</v>
-      </c>
-      <c r="E68" s="16">
-        <v>0</v>
-      </c>
-      <c r="F68" s="10">
-        <v>1081.52</v>
-      </c>
-      <c r="G68" s="16">
-        <v>0</v>
-      </c>
+      <c r="A68" s="15"/>
+      <c r="B68" s="12"/>
+      <c r="C68" s="12"/>
+      <c r="D68" s="10"/>
+      <c r="E68" s="16"/>
+      <c r="F68" s="10"/>
+      <c r="G68" s="16"/>
       <c r="H68" s="17"/>
       <c r="I68" s="4"/>
       <c r="J68" s="4"/>
@@ -3418,27 +2174,13 @@
       <c r="Z68" s="4"/>
     </row>
     <row r="69" spans="1:26">
-      <c r="A69" s="5">
-        <v>46075</v>
-      </c>
-      <c r="B69" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C69" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="D69" s="7">
-        <v>22.48</v>
-      </c>
-      <c r="E69" s="7">
-        <v>1.58</v>
-      </c>
-      <c r="F69" s="7">
-        <v>29.35</v>
-      </c>
-      <c r="G69" s="7">
-        <v>5.29</v>
-      </c>
+      <c r="A69" s="5"/>
+      <c r="B69" s="6"/>
+      <c r="C69" s="6"/>
+      <c r="D69" s="7"/>
+      <c r="E69" s="7"/>
+      <c r="F69" s="7"/>
+      <c r="G69" s="7"/>
       <c r="H69" s="6"/>
       <c r="I69" s="4"/>
       <c r="J69" s="4"/>
@@ -3460,27 +2202,13 @@
       <c r="Z69" s="4"/>
     </row>
     <row r="70" spans="1:26">
-      <c r="A70" s="5">
-        <v>46075</v>
-      </c>
-      <c r="B70" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C70" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="D70" s="7">
-        <v>22.48</v>
-      </c>
-      <c r="E70" s="7">
-        <v>1.58</v>
-      </c>
-      <c r="F70" s="7">
-        <v>29.35</v>
-      </c>
-      <c r="G70" s="7">
-        <v>5.29</v>
-      </c>
+      <c r="A70" s="5"/>
+      <c r="B70" s="6"/>
+      <c r="C70" s="6"/>
+      <c r="D70" s="7"/>
+      <c r="E70" s="7"/>
+      <c r="F70" s="7"/>
+      <c r="G70" s="7"/>
       <c r="H70" s="6"/>
       <c r="I70" s="4"/>
       <c r="J70" s="4"/>
@@ -3502,27 +2230,13 @@
       <c r="Z70" s="4"/>
     </row>
     <row r="71" spans="1:26">
-      <c r="A71" s="15">
-        <v>46075</v>
-      </c>
-      <c r="B71" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="C71" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="D71" s="16">
-        <v>103.66</v>
-      </c>
-      <c r="E71" s="16">
-        <v>0</v>
-      </c>
-      <c r="F71" s="16">
-        <v>103.66</v>
-      </c>
-      <c r="G71" s="16">
-        <v>0</v>
-      </c>
+      <c r="A71" s="15"/>
+      <c r="B71" s="12"/>
+      <c r="C71" s="12"/>
+      <c r="D71" s="16"/>
+      <c r="E71" s="16"/>
+      <c r="F71" s="16"/>
+      <c r="G71" s="16"/>
       <c r="H71" s="17"/>
       <c r="I71" s="4"/>
       <c r="J71" s="4"/>
@@ -3544,142 +2258,58 @@
       <c r="Z71" s="4"/>
     </row>
     <row r="72" spans="1:26">
-      <c r="A72" s="19">
-        <v>46076</v>
-      </c>
-      <c r="B72" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C72" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="D72" s="10">
-        <v>11.57</v>
-      </c>
-      <c r="E72" s="10">
-        <v>0.81</v>
-      </c>
-      <c r="F72" s="10">
-        <v>12.38</v>
-      </c>
-      <c r="G72" s="10">
-        <v>0</v>
-      </c>
+      <c r="A72" s="19"/>
+      <c r="B72" s="6"/>
+      <c r="C72" s="6"/>
+      <c r="D72" s="10"/>
+      <c r="E72" s="10"/>
+      <c r="F72" s="10"/>
+      <c r="G72" s="10"/>
     </row>
     <row r="73" spans="1:26">
-      <c r="A73" s="19">
-        <v>46076</v>
-      </c>
-      <c r="B73" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="C73" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="D73" s="10">
-        <v>86.65</v>
-      </c>
-      <c r="E73" s="10">
-        <v>0</v>
-      </c>
-      <c r="F73" s="10">
-        <v>86.65</v>
-      </c>
-      <c r="G73" s="10">
-        <v>0</v>
-      </c>
+      <c r="A73" s="19"/>
+      <c r="B73" s="6"/>
+      <c r="C73" s="6"/>
+      <c r="D73" s="10"/>
+      <c r="E73" s="10"/>
+      <c r="F73" s="10"/>
+      <c r="G73" s="10"/>
     </row>
     <row r="74" spans="1:26">
-      <c r="A74" s="19">
-        <v>46079</v>
-      </c>
-      <c r="B74" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C74" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="D74" s="10">
-        <v>6.25</v>
-      </c>
-      <c r="E74" s="10">
-        <v>0.44</v>
-      </c>
-      <c r="F74" s="10">
-        <v>8.69</v>
-      </c>
-      <c r="G74" s="10">
-        <v>2</v>
-      </c>
+      <c r="A74" s="19"/>
+      <c r="B74" s="6"/>
+      <c r="C74" s="6"/>
+      <c r="D74" s="10"/>
+      <c r="E74" s="10"/>
+      <c r="F74" s="10"/>
+      <c r="G74" s="10"/>
     </row>
     <row r="75" spans="1:26">
-      <c r="A75" s="19">
-        <v>46079</v>
-      </c>
-      <c r="B75" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C75" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="D75" s="10">
-        <v>47.61</v>
-      </c>
-      <c r="E75" s="10">
-        <v>0.38</v>
-      </c>
-      <c r="F75" s="10">
-        <v>47.99</v>
-      </c>
-      <c r="G75" s="10">
-        <v>0</v>
-      </c>
+      <c r="A75" s="19"/>
+      <c r="B75" s="6"/>
+      <c r="C75" s="6"/>
+      <c r="D75" s="10"/>
+      <c r="E75" s="10"/>
+      <c r="F75" s="10"/>
+      <c r="G75" s="10"/>
     </row>
     <row r="76" spans="1:26">
-      <c r="A76" s="19">
-        <v>46079</v>
-      </c>
-      <c r="B76" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C76" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="D76" s="10">
-        <v>22.88</v>
-      </c>
-      <c r="E76" s="10">
-        <v>1.61</v>
-      </c>
-      <c r="F76" s="10">
-        <v>29.88</v>
-      </c>
-      <c r="G76" s="10">
-        <v>5.39</v>
-      </c>
+      <c r="A76" s="19"/>
+      <c r="B76" s="6"/>
+      <c r="C76" s="6"/>
+      <c r="D76" s="10"/>
+      <c r="E76" s="10"/>
+      <c r="F76" s="10"/>
+      <c r="G76" s="10"/>
     </row>
     <row r="77" spans="1:26">
-      <c r="A77" s="5">
-        <v>46079</v>
-      </c>
-      <c r="B77" s="12" t="s">
-        <v>63</v>
-      </c>
-      <c r="C77" s="12" t="s">
-        <v>61</v>
-      </c>
-      <c r="D77" s="14">
-        <v>382.8</v>
-      </c>
-      <c r="E77" s="16">
-        <v>0</v>
-      </c>
-      <c r="F77" s="14">
-        <v>382.8</v>
-      </c>
-      <c r="G77" s="16">
-        <v>0</v>
-      </c>
+      <c r="A77" s="5"/>
+      <c r="B77" s="12"/>
+      <c r="C77" s="12"/>
+      <c r="D77" s="14"/>
+      <c r="E77" s="16"/>
+      <c r="F77" s="14"/>
+      <c r="G77" s="16"/>
       <c r="H77" s="6"/>
       <c r="I77" s="4"/>
       <c r="J77" s="4"/>
@@ -3701,27 +2331,13 @@
       <c r="Z77" s="4"/>
     </row>
     <row r="78" spans="1:26">
-      <c r="A78" s="15">
-        <v>46079</v>
-      </c>
-      <c r="B78" s="12" t="s">
-        <v>60</v>
-      </c>
-      <c r="C78" s="12" t="s">
-        <v>61</v>
-      </c>
-      <c r="D78" s="16">
-        <v>169.68</v>
-      </c>
-      <c r="E78" s="16">
-        <v>0</v>
-      </c>
-      <c r="F78" s="16">
-        <v>169.68</v>
-      </c>
-      <c r="G78" s="16">
-        <v>0</v>
-      </c>
+      <c r="A78" s="15"/>
+      <c r="B78" s="12"/>
+      <c r="C78" s="12"/>
+      <c r="D78" s="16"/>
+      <c r="E78" s="16"/>
+      <c r="F78" s="16"/>
+      <c r="G78" s="16"/>
       <c r="H78" s="17"/>
       <c r="I78" s="4"/>
       <c r="J78" s="4"/>
@@ -3743,96 +2359,40 @@
       <c r="Z78" s="4"/>
     </row>
     <row r="79" spans="1:26">
-      <c r="A79" s="19">
-        <v>46080</v>
-      </c>
-      <c r="B79" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="C79" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="D79" s="10">
-        <v>29.98</v>
-      </c>
-      <c r="E79" s="10">
-        <v>0</v>
-      </c>
-      <c r="F79" s="10">
-        <v>31.93</v>
-      </c>
-      <c r="G79" s="10">
-        <v>0</v>
-      </c>
+      <c r="A79" s="19"/>
+      <c r="B79" s="6"/>
+      <c r="C79" s="6"/>
+      <c r="D79" s="10"/>
+      <c r="E79" s="10"/>
+      <c r="F79" s="10"/>
+      <c r="G79" s="10"/>
     </row>
     <row r="80" spans="1:26">
-      <c r="A80" s="19">
-        <v>46082</v>
-      </c>
-      <c r="B80" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C80" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="D80" s="10">
-        <v>23.22</v>
-      </c>
-      <c r="E80" s="10">
-        <v>0</v>
-      </c>
-      <c r="F80" s="10">
-        <v>23.22</v>
-      </c>
-      <c r="G80" s="10">
-        <v>3.87</v>
-      </c>
+      <c r="A80" s="19"/>
+      <c r="B80" s="6"/>
+      <c r="C80" s="6"/>
+      <c r="D80" s="10"/>
+      <c r="E80" s="10"/>
+      <c r="F80" s="10"/>
+      <c r="G80" s="10"/>
     </row>
     <row r="81" spans="1:26">
-      <c r="A81" s="19">
-        <v>46082</v>
-      </c>
-      <c r="B81" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C81" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="D81" s="10">
-        <v>18.079999999999998</v>
-      </c>
-      <c r="E81" s="10">
-        <v>1.27</v>
-      </c>
-      <c r="F81" s="10">
-        <v>23.22</v>
-      </c>
-      <c r="G81" s="10">
-        <v>3.87</v>
-      </c>
+      <c r="A81" s="19"/>
+      <c r="B81" s="6"/>
+      <c r="C81" s="6"/>
+      <c r="D81" s="10"/>
+      <c r="E81" s="10"/>
+      <c r="F81" s="10"/>
+      <c r="G81" s="10"/>
     </row>
     <row r="82" spans="1:26">
-      <c r="A82" s="11">
-        <v>46082</v>
-      </c>
-      <c r="B82" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="C82" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="D82" s="10">
-        <v>886.7</v>
-      </c>
-      <c r="E82" s="7">
-        <v>0</v>
-      </c>
-      <c r="F82" s="10">
-        <v>886.7</v>
-      </c>
-      <c r="G82" s="7">
-        <v>0</v>
-      </c>
+      <c r="A82" s="11"/>
+      <c r="B82" s="6"/>
+      <c r="C82" s="6"/>
+      <c r="D82" s="10"/>
+      <c r="E82" s="7"/>
+      <c r="F82" s="10"/>
+      <c r="G82" s="7"/>
       <c r="H82" s="6"/>
       <c r="I82" s="12"/>
       <c r="J82" s="4"/>
@@ -3854,27 +2414,13 @@
       <c r="Z82" s="4"/>
     </row>
     <row r="83" spans="1:26">
-      <c r="A83" s="15">
-        <v>46082</v>
-      </c>
-      <c r="B83" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="C83" s="12" t="s">
-        <v>83</v>
-      </c>
-      <c r="D83" s="16">
-        <v>385</v>
-      </c>
-      <c r="E83" s="16">
-        <v>51.98</v>
-      </c>
-      <c r="F83" s="16">
-        <v>436.98</v>
-      </c>
-      <c r="G83" s="16">
-        <v>0</v>
-      </c>
+      <c r="A83" s="15"/>
+      <c r="B83" s="6"/>
+      <c r="C83" s="12"/>
+      <c r="D83" s="16"/>
+      <c r="E83" s="16"/>
+      <c r="F83" s="16"/>
+      <c r="G83" s="16"/>
       <c r="H83" s="17"/>
       <c r="I83" s="4"/>
       <c r="J83" s="4"/>
@@ -3896,27 +2442,13 @@
       <c r="Z83" s="4"/>
     </row>
     <row r="84" spans="1:26">
-      <c r="A84" s="11">
-        <v>46083</v>
-      </c>
-      <c r="B84" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="C84" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="D84" s="14">
-        <v>28.29</v>
-      </c>
-      <c r="E84" s="7">
-        <v>0</v>
-      </c>
-      <c r="F84" s="14">
-        <v>28.29</v>
-      </c>
-      <c r="G84" s="7">
-        <v>0</v>
-      </c>
+      <c r="A84" s="11"/>
+      <c r="B84" s="12"/>
+      <c r="C84" s="13"/>
+      <c r="D84" s="14"/>
+      <c r="E84" s="7"/>
+      <c r="F84" s="14"/>
+      <c r="G84" s="7"/>
       <c r="H84" s="6"/>
       <c r="I84" s="4"/>
       <c r="J84" s="4"/>
@@ -3938,27 +2470,13 @@
       <c r="Z84" s="4"/>
     </row>
     <row r="85" spans="1:26">
-      <c r="A85" s="11">
-        <v>46083</v>
-      </c>
-      <c r="B85" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C85" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="D85" s="7">
-        <v>17.97</v>
-      </c>
-      <c r="E85" s="7">
-        <v>1.35</v>
-      </c>
-      <c r="F85" s="7">
-        <v>19.32</v>
-      </c>
-      <c r="G85" s="7">
-        <v>0</v>
-      </c>
+      <c r="A85" s="11"/>
+      <c r="B85" s="6"/>
+      <c r="C85" s="6"/>
+      <c r="D85" s="7"/>
+      <c r="E85" s="7"/>
+      <c r="F85" s="7"/>
+      <c r="G85" s="7"/>
       <c r="H85" s="6"/>
       <c r="I85" s="4"/>
       <c r="J85" s="4"/>
@@ -3980,27 +2498,13 @@
       <c r="Z85" s="4"/>
     </row>
     <row r="86" spans="1:26">
-      <c r="A86" s="11">
-        <v>46083</v>
-      </c>
-      <c r="B86" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C86" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="D86" s="7">
-        <v>90.73</v>
-      </c>
-      <c r="E86" s="7">
-        <v>2.64</v>
-      </c>
-      <c r="F86" s="7">
-        <v>93.37</v>
-      </c>
-      <c r="G86" s="7">
-        <v>0</v>
-      </c>
+      <c r="A86" s="11"/>
+      <c r="B86" s="6"/>
+      <c r="C86" s="6"/>
+      <c r="D86" s="7"/>
+      <c r="E86" s="7"/>
+      <c r="F86" s="7"/>
+      <c r="G86" s="7"/>
       <c r="H86" s="6"/>
       <c r="I86" s="4"/>
       <c r="J86" s="4"/>
@@ -4022,27 +2526,13 @@
       <c r="Z86" s="4"/>
     </row>
     <row r="87" spans="1:26">
-      <c r="A87" s="11">
-        <v>46083</v>
-      </c>
-      <c r="B87" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C87" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="D87" s="7">
-        <v>18.649999999999999</v>
-      </c>
-      <c r="E87" s="7">
-        <v>1.4</v>
-      </c>
-      <c r="F87" s="7">
-        <v>20.05</v>
-      </c>
-      <c r="G87" s="7">
-        <v>3</v>
-      </c>
+      <c r="A87" s="11"/>
+      <c r="B87" s="6"/>
+      <c r="C87" s="6"/>
+      <c r="D87" s="7"/>
+      <c r="E87" s="7"/>
+      <c r="F87" s="7"/>
+      <c r="G87" s="7"/>
       <c r="H87" s="6"/>
       <c r="I87" s="4"/>
       <c r="J87" s="4"/>
@@ -4064,27 +2554,13 @@
       <c r="Z87" s="4"/>
     </row>
     <row r="88" spans="1:26">
-      <c r="A88" s="11">
-        <v>46083</v>
-      </c>
-      <c r="B88" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C88" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="D88" s="7">
-        <v>8.98</v>
-      </c>
-      <c r="E88" s="7">
-        <v>0.67</v>
-      </c>
-      <c r="F88" s="7">
-        <v>11.65</v>
-      </c>
-      <c r="G88" s="7">
-        <v>2</v>
-      </c>
+      <c r="A88" s="11"/>
+      <c r="B88" s="6"/>
+      <c r="C88" s="6"/>
+      <c r="D88" s="7"/>
+      <c r="E88" s="7"/>
+      <c r="F88" s="7"/>
+      <c r="G88" s="7"/>
       <c r="H88" s="6"/>
       <c r="I88" s="4"/>
       <c r="J88" s="4"/>
@@ -4106,27 +2582,13 @@
       <c r="Z88" s="4"/>
     </row>
     <row r="89" spans="1:26">
-      <c r="A89" s="11">
-        <v>46084</v>
-      </c>
-      <c r="B89" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C89" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="D89" s="7">
-        <v>16.18</v>
-      </c>
-      <c r="E89" s="7">
-        <v>1.21</v>
-      </c>
-      <c r="F89" s="7">
-        <v>19.39</v>
-      </c>
-      <c r="G89" s="7">
-        <v>2</v>
-      </c>
+      <c r="A89" s="11"/>
+      <c r="B89" s="6"/>
+      <c r="C89" s="6"/>
+      <c r="D89" s="7"/>
+      <c r="E89" s="7"/>
+      <c r="F89" s="7"/>
+      <c r="G89" s="7"/>
       <c r="H89" s="6"/>
       <c r="I89" s="4"/>
       <c r="J89" s="4"/>
@@ -4148,27 +2610,13 @@
       <c r="Z89" s="4"/>
     </row>
     <row r="90" spans="1:26">
-      <c r="A90" s="11">
-        <v>46085</v>
-      </c>
-      <c r="B90" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C90" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="D90" s="7">
-        <v>29.99</v>
-      </c>
-      <c r="E90" s="7">
-        <v>2.25</v>
-      </c>
-      <c r="F90" s="7">
-        <v>38.630000000000003</v>
-      </c>
-      <c r="G90" s="7">
-        <v>6.39</v>
-      </c>
+      <c r="A90" s="11"/>
+      <c r="B90" s="6"/>
+      <c r="C90" s="6"/>
+      <c r="D90" s="7"/>
+      <c r="E90" s="7"/>
+      <c r="F90" s="7"/>
+      <c r="G90" s="7"/>
       <c r="H90" s="6"/>
       <c r="I90" s="4"/>
       <c r="J90" s="4"/>
@@ -4190,27 +2638,13 @@
       <c r="Z90" s="4"/>
     </row>
     <row r="91" spans="1:26">
-      <c r="A91" s="11">
-        <v>46085</v>
-      </c>
-      <c r="B91" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="C91" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="D91" s="14">
-        <v>36</v>
-      </c>
-      <c r="E91" s="7">
-        <v>0</v>
-      </c>
-      <c r="F91" s="14">
-        <v>36</v>
-      </c>
-      <c r="G91" s="7">
-        <v>0</v>
-      </c>
+      <c r="A91" s="11"/>
+      <c r="B91" s="6"/>
+      <c r="C91" s="6"/>
+      <c r="D91" s="14"/>
+      <c r="E91" s="7"/>
+      <c r="F91" s="14"/>
+      <c r="G91" s="7"/>
       <c r="H91" s="6"/>
       <c r="I91" s="4"/>
       <c r="J91" s="4"/>
@@ -4232,50 +2666,22 @@
       <c r="Z91" s="4"/>
     </row>
     <row r="92" spans="1:26">
-      <c r="A92" s="19">
-        <v>46085</v>
-      </c>
-      <c r="B92" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C92" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="D92" s="10">
-        <v>29.99</v>
-      </c>
-      <c r="E92" s="10">
-        <v>2.25</v>
-      </c>
-      <c r="F92" s="10">
-        <v>38.630000000000003</v>
-      </c>
-      <c r="G92" s="10">
-        <v>6.39</v>
-      </c>
+      <c r="A92" s="19"/>
+      <c r="B92" s="6"/>
+      <c r="C92" s="6"/>
+      <c r="D92" s="10"/>
+      <c r="E92" s="10"/>
+      <c r="F92" s="10"/>
+      <c r="G92" s="10"/>
     </row>
     <row r="93" spans="1:26">
-      <c r="A93" s="11">
-        <v>46086</v>
-      </c>
-      <c r="B93" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C93" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="D93" s="7">
-        <v>0</v>
-      </c>
-      <c r="E93" s="7">
-        <v>0</v>
-      </c>
-      <c r="F93" s="7">
-        <v>27.31</v>
-      </c>
-      <c r="G93" s="7">
-        <v>3.56</v>
-      </c>
+      <c r="A93" s="11"/>
+      <c r="B93" s="6"/>
+      <c r="C93" s="6"/>
+      <c r="D93" s="7"/>
+      <c r="E93" s="7"/>
+      <c r="F93" s="7"/>
+      <c r="G93" s="7"/>
       <c r="H93" s="6"/>
       <c r="I93" s="4"/>
       <c r="J93" s="4"/>
@@ -4297,27 +2703,13 @@
       <c r="Z93" s="4"/>
     </row>
     <row r="94" spans="1:26">
-      <c r="A94" s="11">
-        <v>46086</v>
-      </c>
-      <c r="B94" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C94" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="D94" s="7">
-        <v>22.37</v>
-      </c>
-      <c r="E94" s="7">
-        <v>1.38</v>
-      </c>
-      <c r="F94" s="7">
-        <v>27.31</v>
-      </c>
-      <c r="G94" s="7">
-        <v>3.56</v>
-      </c>
+      <c r="A94" s="11"/>
+      <c r="B94" s="6"/>
+      <c r="C94" s="6"/>
+      <c r="D94" s="7"/>
+      <c r="E94" s="7"/>
+      <c r="F94" s="7"/>
+      <c r="G94" s="7"/>
       <c r="H94" s="6"/>
       <c r="I94" s="4"/>
       <c r="J94" s="4"/>
@@ -4339,27 +2731,13 @@
       <c r="Z94" s="4"/>
     </row>
     <row r="95" spans="1:26">
-      <c r="A95" s="11">
-        <v>46087</v>
-      </c>
-      <c r="B95" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C95" s="6" t="s">
-        <v>88</v>
-      </c>
-      <c r="D95" s="7">
-        <v>12.99</v>
-      </c>
-      <c r="E95" s="7">
-        <v>0.97</v>
-      </c>
-      <c r="F95" s="7">
-        <v>13.96</v>
-      </c>
-      <c r="G95" s="7">
-        <v>0</v>
-      </c>
+      <c r="A95" s="11"/>
+      <c r="B95" s="6"/>
+      <c r="C95" s="6"/>
+      <c r="D95" s="7"/>
+      <c r="E95" s="7"/>
+      <c r="F95" s="7"/>
+      <c r="G95" s="7"/>
       <c r="H95" s="6"/>
       <c r="I95" s="4"/>
       <c r="J95" s="4"/>
@@ -4381,27 +2759,13 @@
       <c r="Z95" s="4"/>
     </row>
     <row r="96" spans="1:26">
-      <c r="A96" s="11">
-        <v>46087</v>
-      </c>
-      <c r="B96" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C96" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="D96" s="7">
-        <v>12.8</v>
-      </c>
-      <c r="E96" s="7">
-        <v>0.96</v>
-      </c>
-      <c r="F96" s="7">
-        <v>14.76</v>
-      </c>
-      <c r="G96" s="7">
-        <v>1</v>
-      </c>
+      <c r="A96" s="11"/>
+      <c r="B96" s="6"/>
+      <c r="C96" s="6"/>
+      <c r="D96" s="7"/>
+      <c r="E96" s="7"/>
+      <c r="F96" s="7"/>
+      <c r="G96" s="7"/>
       <c r="H96" s="6"/>
       <c r="I96" s="4"/>
       <c r="J96" s="4"/>
@@ -4423,27 +2787,13 @@
       <c r="Z96" s="4"/>
     </row>
     <row r="97" spans="1:26">
-      <c r="A97" s="11">
-        <v>46088</v>
-      </c>
-      <c r="B97" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C97" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="D97" s="7">
-        <v>11.78</v>
-      </c>
-      <c r="E97" s="7">
-        <v>0</v>
-      </c>
-      <c r="F97" s="7">
-        <v>11.78</v>
-      </c>
-      <c r="G97" s="7">
-        <v>0</v>
-      </c>
+      <c r="A97" s="11"/>
+      <c r="B97" s="6"/>
+      <c r="C97" s="6"/>
+      <c r="D97" s="7"/>
+      <c r="E97" s="7"/>
+      <c r="F97" s="7"/>
+      <c r="G97" s="7"/>
       <c r="H97" s="6"/>
       <c r="I97" s="4"/>
       <c r="J97" s="4"/>
@@ -4465,50 +2815,22 @@
       <c r="Z97" s="4"/>
     </row>
     <row r="98" spans="1:26">
-      <c r="A98" s="19">
-        <v>46088</v>
-      </c>
-      <c r="B98" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="C98" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="D98" s="10">
-        <v>58.72</v>
-      </c>
-      <c r="E98" s="10">
-        <v>0</v>
-      </c>
-      <c r="F98" s="10">
-        <v>58.72</v>
-      </c>
-      <c r="G98" s="10">
-        <v>0</v>
-      </c>
+      <c r="A98" s="19"/>
+      <c r="B98" s="6"/>
+      <c r="C98" s="6"/>
+      <c r="D98" s="10"/>
+      <c r="E98" s="10"/>
+      <c r="F98" s="10"/>
+      <c r="G98" s="10"/>
     </row>
     <row r="99" spans="1:26">
-      <c r="A99" s="15">
-        <v>46088</v>
-      </c>
-      <c r="B99" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="C99" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="D99" s="14">
-        <v>318</v>
-      </c>
-      <c r="E99" s="16">
-        <v>0</v>
-      </c>
-      <c r="F99" s="14">
-        <v>318</v>
-      </c>
-      <c r="G99" s="16">
-        <v>0</v>
-      </c>
+      <c r="A99" s="15"/>
+      <c r="B99" s="12"/>
+      <c r="C99" s="13"/>
+      <c r="D99" s="14"/>
+      <c r="E99" s="16"/>
+      <c r="F99" s="14"/>
+      <c r="G99" s="16"/>
       <c r="H99" s="17"/>
       <c r="I99" s="4"/>
       <c r="J99" s="4"/>
@@ -4530,119 +2852,49 @@
       <c r="Z99" s="4"/>
     </row>
     <row r="100" spans="1:26">
-      <c r="A100" s="15">
-        <v>46089</v>
-      </c>
-      <c r="B100" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="C100" s="12" t="s">
-        <v>72</v>
-      </c>
-      <c r="D100" s="16">
-        <v>472.43</v>
-      </c>
-      <c r="E100" s="16">
-        <v>71.680000000000007</v>
-      </c>
-      <c r="F100" s="16">
-        <v>544.11</v>
-      </c>
-      <c r="G100" s="16">
-        <v>0</v>
-      </c>
+      <c r="A100" s="15"/>
+      <c r="B100" s="6"/>
+      <c r="C100" s="12"/>
+      <c r="D100" s="16"/>
+      <c r="E100" s="16"/>
+      <c r="F100" s="16"/>
+      <c r="G100" s="16"/>
     </row>
     <row r="101" spans="1:26">
-      <c r="A101" s="19">
-        <v>46089</v>
-      </c>
-      <c r="B101" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C101" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="D101" s="10">
-        <v>10.98</v>
-      </c>
-      <c r="E101" s="10">
-        <v>0.59</v>
-      </c>
-      <c r="F101" s="10">
-        <v>11.57</v>
-      </c>
-      <c r="G101" s="10">
-        <v>0</v>
-      </c>
+      <c r="A101" s="19"/>
+      <c r="B101" s="6"/>
+      <c r="C101" s="6"/>
+      <c r="D101" s="10"/>
+      <c r="E101" s="10"/>
+      <c r="F101" s="10"/>
+      <c r="G101" s="10"/>
     </row>
     <row r="102" spans="1:26">
-      <c r="A102" s="19">
-        <v>46089</v>
-      </c>
-      <c r="B102" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C102" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="D102" s="10">
-        <v>6.49</v>
-      </c>
-      <c r="E102" s="10">
-        <v>0.45</v>
-      </c>
-      <c r="F102" s="10">
-        <v>7.94</v>
-      </c>
-      <c r="G102" s="10">
-        <v>1</v>
-      </c>
+      <c r="A102" s="19"/>
+      <c r="B102" s="6"/>
+      <c r="C102" s="6"/>
+      <c r="D102" s="10"/>
+      <c r="E102" s="10"/>
+      <c r="F102" s="10"/>
+      <c r="G102" s="10"/>
     </row>
     <row r="103" spans="1:26">
-      <c r="A103" s="19">
-        <v>46089</v>
-      </c>
-      <c r="B103" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C103" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="D103" s="10">
-        <v>12.48</v>
-      </c>
-      <c r="E103" s="10">
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="F103" s="10">
-        <v>12.62</v>
-      </c>
-      <c r="G103" s="10">
-        <v>0</v>
-      </c>
+      <c r="A103" s="19"/>
+      <c r="B103" s="6"/>
+      <c r="C103" s="6"/>
+      <c r="D103" s="10"/>
+      <c r="E103" s="10"/>
+      <c r="F103" s="10"/>
+      <c r="G103" s="10"/>
     </row>
     <row r="104" spans="1:26">
-      <c r="A104" s="15">
-        <v>46089</v>
-      </c>
-      <c r="B104" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="C104" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="D104" s="16">
-        <v>195.47</v>
-      </c>
-      <c r="E104" s="16">
-        <v>0</v>
-      </c>
-      <c r="F104" s="16">
-        <v>195.47</v>
-      </c>
-      <c r="G104" s="16">
-        <v>0</v>
-      </c>
+      <c r="A104" s="15"/>
+      <c r="B104" s="12"/>
+      <c r="C104" s="12"/>
+      <c r="D104" s="16"/>
+      <c r="E104" s="16"/>
+      <c r="F104" s="16"/>
+      <c r="G104" s="16"/>
       <c r="H104" s="17"/>
       <c r="I104" s="4"/>
       <c r="J104" s="4"/>
@@ -4664,27 +2916,13 @@
       <c r="Z104" s="4"/>
     </row>
     <row r="105" spans="1:26">
-      <c r="A105" s="11">
-        <v>46090</v>
-      </c>
-      <c r="B105" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C105" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="D105" s="7">
-        <v>15.88</v>
-      </c>
-      <c r="E105" s="7">
-        <v>1.1100000000000001</v>
-      </c>
-      <c r="F105" s="7">
-        <v>20.05</v>
-      </c>
-      <c r="G105" s="7">
-        <v>3.06</v>
-      </c>
+      <c r="A105" s="11"/>
+      <c r="B105" s="6"/>
+      <c r="C105" s="6"/>
+      <c r="D105" s="7"/>
+      <c r="E105" s="7"/>
+      <c r="F105" s="7"/>
+      <c r="G105" s="7"/>
       <c r="H105" s="6"/>
       <c r="I105" s="4"/>
       <c r="J105" s="4"/>
@@ -4706,27 +2944,13 @@
       <c r="Z105" s="4"/>
     </row>
     <row r="106" spans="1:26">
-      <c r="A106" s="11">
-        <v>46091</v>
-      </c>
-      <c r="B106" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="C106" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="D106" s="14">
-        <v>39</v>
-      </c>
-      <c r="E106" s="16">
-        <v>0</v>
-      </c>
-      <c r="F106" s="14">
-        <v>39</v>
-      </c>
-      <c r="G106" s="16">
-        <v>0</v>
-      </c>
+      <c r="A106" s="11"/>
+      <c r="B106" s="12"/>
+      <c r="C106" s="6"/>
+      <c r="D106" s="14"/>
+      <c r="E106" s="16"/>
+      <c r="F106" s="14"/>
+      <c r="G106" s="16"/>
       <c r="H106" s="6"/>
       <c r="I106" s="4"/>
       <c r="J106" s="4"/>
@@ -4748,27 +2972,13 @@
       <c r="Z106" s="4"/>
     </row>
     <row r="107" spans="1:26">
-      <c r="A107" s="11">
-        <v>46091</v>
-      </c>
-      <c r="B107" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C107" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="D107" s="7">
-        <v>21.46</v>
-      </c>
-      <c r="E107" s="7">
-        <v>1.5</v>
-      </c>
-      <c r="F107" s="7">
-        <v>22.96</v>
-      </c>
-      <c r="G107" s="7">
-        <v>0</v>
-      </c>
+      <c r="A107" s="11"/>
+      <c r="B107" s="6"/>
+      <c r="C107" s="6"/>
+      <c r="D107" s="7"/>
+      <c r="E107" s="7"/>
+      <c r="F107" s="7"/>
+      <c r="G107" s="7"/>
       <c r="H107" s="6"/>
       <c r="I107" s="4"/>
       <c r="J107" s="4"/>
@@ -4790,27 +3000,13 @@
       <c r="Z107" s="4"/>
     </row>
     <row r="108" spans="1:26">
-      <c r="A108" s="11">
-        <v>46094</v>
-      </c>
-      <c r="B108" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C108" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="D108" s="7">
-        <v>6.49</v>
-      </c>
-      <c r="E108" s="7">
-        <v>0.45</v>
-      </c>
-      <c r="F108" s="7">
-        <v>6.94</v>
-      </c>
-      <c r="G108" s="7">
-        <v>0</v>
-      </c>
+      <c r="A108" s="11"/>
+      <c r="B108" s="6"/>
+      <c r="C108" s="6"/>
+      <c r="D108" s="7"/>
+      <c r="E108" s="7"/>
+      <c r="F108" s="7"/>
+      <c r="G108" s="7"/>
       <c r="H108" s="6"/>
       <c r="I108" s="4"/>
       <c r="J108" s="4"/>
@@ -4832,27 +3028,13 @@
       <c r="Z108" s="4"/>
     </row>
     <row r="109" spans="1:26">
-      <c r="A109" s="5">
-        <v>46094</v>
-      </c>
-      <c r="B109" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C109" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="D109" s="7">
-        <v>0</v>
-      </c>
-      <c r="E109" s="7">
-        <v>0</v>
-      </c>
-      <c r="F109" s="7">
-        <v>16.46</v>
-      </c>
-      <c r="G109" s="7">
-        <v>0</v>
-      </c>
+      <c r="A109" s="5"/>
+      <c r="B109" s="6"/>
+      <c r="C109" s="6"/>
+      <c r="D109" s="7"/>
+      <c r="E109" s="7"/>
+      <c r="F109" s="7"/>
+      <c r="G109" s="7"/>
       <c r="H109" s="6"/>
       <c r="I109" s="4"/>
       <c r="J109" s="4"/>
@@ -4874,27 +3056,13 @@
       <c r="Z109" s="4"/>
     </row>
     <row r="110" spans="1:26">
-      <c r="A110" s="11">
-        <v>46094</v>
-      </c>
-      <c r="B110" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C110" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="D110" s="7">
-        <v>15.38</v>
-      </c>
-      <c r="E110" s="7">
-        <v>1.08</v>
-      </c>
-      <c r="F110" s="7">
-        <v>16.46</v>
-      </c>
-      <c r="G110" s="7">
-        <v>0</v>
-      </c>
+      <c r="A110" s="11"/>
+      <c r="B110" s="6"/>
+      <c r="C110" s="6"/>
+      <c r="D110" s="7"/>
+      <c r="E110" s="7"/>
+      <c r="F110" s="7"/>
+      <c r="G110" s="7"/>
       <c r="H110" s="6"/>
       <c r="I110" s="4"/>
       <c r="J110" s="4"/>
@@ -4916,27 +3084,13 @@
       <c r="Z110" s="4"/>
     </row>
     <row r="111" spans="1:26">
-      <c r="A111" s="5">
-        <v>46094</v>
-      </c>
-      <c r="B111" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C111" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="D111" s="7">
-        <v>3.89</v>
-      </c>
-      <c r="E111" s="7">
-        <v>0</v>
-      </c>
-      <c r="F111" s="7">
-        <v>3.89</v>
-      </c>
-      <c r="G111" s="7">
-        <v>0</v>
-      </c>
+      <c r="A111" s="5"/>
+      <c r="B111" s="6"/>
+      <c r="C111" s="6"/>
+      <c r="D111" s="7"/>
+      <c r="E111" s="7"/>
+      <c r="F111" s="7"/>
+      <c r="G111" s="7"/>
       <c r="H111" s="6"/>
       <c r="I111" s="4"/>
       <c r="J111" s="4"/>
@@ -4958,27 +3112,13 @@
       <c r="Z111" s="4"/>
     </row>
     <row r="112" spans="1:26">
-      <c r="A112" s="15">
-        <v>46094</v>
-      </c>
-      <c r="B112" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="C112" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="D112" s="16">
-        <v>101</v>
-      </c>
-      <c r="E112" s="16">
-        <v>0</v>
-      </c>
-      <c r="F112" s="16">
-        <v>101</v>
-      </c>
-      <c r="G112" s="16">
-        <v>0</v>
-      </c>
+      <c r="A112" s="15"/>
+      <c r="B112" s="12"/>
+      <c r="C112" s="12"/>
+      <c r="D112" s="16"/>
+      <c r="E112" s="16"/>
+      <c r="F112" s="16"/>
+      <c r="G112" s="16"/>
       <c r="H112" s="17"/>
       <c r="I112" s="4"/>
       <c r="J112" s="4"/>
@@ -5000,27 +3140,13 @@
       <c r="Z112" s="4"/>
     </row>
     <row r="113" spans="1:26">
-      <c r="A113" s="15">
-        <v>46095</v>
-      </c>
-      <c r="B113" s="12" t="s">
-        <v>56</v>
-      </c>
-      <c r="C113" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="D113" s="14">
-        <v>1366.06</v>
-      </c>
-      <c r="E113" s="16">
-        <v>0</v>
-      </c>
-      <c r="F113" s="14">
-        <v>1366.06</v>
-      </c>
-      <c r="G113" s="16">
-        <v>0</v>
-      </c>
+      <c r="A113" s="15"/>
+      <c r="B113" s="12"/>
+      <c r="C113" s="12"/>
+      <c r="D113" s="14"/>
+      <c r="E113" s="16"/>
+      <c r="F113" s="14"/>
+      <c r="G113" s="16"/>
       <c r="H113" s="17"/>
       <c r="I113" s="4"/>
       <c r="J113" s="4"/>
@@ -5042,27 +3168,13 @@
       <c r="Z113" s="4"/>
     </row>
     <row r="114" spans="1:26">
-      <c r="A114" s="5">
-        <v>46095</v>
-      </c>
-      <c r="B114" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C114" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="D114" s="7">
-        <v>118.61</v>
-      </c>
-      <c r="E114" s="7">
-        <v>2.97</v>
-      </c>
-      <c r="F114" s="7">
-        <v>121.58</v>
-      </c>
-      <c r="G114" s="7">
-        <v>0</v>
-      </c>
+      <c r="A114" s="5"/>
+      <c r="B114" s="6"/>
+      <c r="C114" s="6"/>
+      <c r="D114" s="7"/>
+      <c r="E114" s="7"/>
+      <c r="F114" s="7"/>
+      <c r="G114" s="7"/>
       <c r="H114" s="6"/>
       <c r="I114" s="4"/>
       <c r="J114" s="4"/>
@@ -5084,27 +3196,13 @@
       <c r="Z114" s="4"/>
     </row>
     <row r="115" spans="1:26">
-      <c r="A115" s="11">
-        <v>46095</v>
-      </c>
-      <c r="B115" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C115" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="D115" s="7">
-        <v>3.39</v>
-      </c>
-      <c r="E115" s="7">
-        <v>0.24</v>
-      </c>
-      <c r="F115" s="7">
-        <v>3.63</v>
-      </c>
-      <c r="G115" s="7">
-        <v>0</v>
-      </c>
+      <c r="A115" s="11"/>
+      <c r="B115" s="6"/>
+      <c r="C115" s="6"/>
+      <c r="D115" s="7"/>
+      <c r="E115" s="7"/>
+      <c r="F115" s="7"/>
+      <c r="G115" s="7"/>
       <c r="H115" s="6"/>
       <c r="I115" s="4"/>
       <c r="J115" s="4"/>
@@ -5126,27 +3224,13 @@
       <c r="Z115" s="4"/>
     </row>
     <row r="116" spans="1:26">
-      <c r="A116" s="15">
-        <v>46068</v>
-      </c>
-      <c r="B116" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="C116" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="D116" s="20">
-        <v>280</v>
-      </c>
-      <c r="E116" s="16">
-        <v>0</v>
-      </c>
-      <c r="F116" s="20">
-        <v>280</v>
-      </c>
-      <c r="G116" s="16">
-        <v>0</v>
-      </c>
+      <c r="A116" s="15"/>
+      <c r="B116" s="12"/>
+      <c r="C116" s="13"/>
+      <c r="D116" s="20"/>
+      <c r="E116" s="16"/>
+      <c r="F116" s="20"/>
+      <c r="G116" s="16"/>
       <c r="H116" s="17"/>
       <c r="I116" s="4"/>
       <c r="J116" s="4"/>
@@ -5168,27 +3252,13 @@
       <c r="Z116" s="4"/>
     </row>
     <row r="117" spans="1:26">
-      <c r="A117" s="15">
-        <v>46096</v>
-      </c>
-      <c r="B117" s="12" t="s">
-        <v>56</v>
-      </c>
-      <c r="C117" s="12" t="s">
-        <v>57</v>
-      </c>
-      <c r="D117" s="10">
-        <v>1500</v>
-      </c>
-      <c r="E117" s="16">
-        <v>0</v>
-      </c>
-      <c r="F117" s="10">
-        <v>1500</v>
-      </c>
-      <c r="G117" s="16">
-        <v>0</v>
-      </c>
+      <c r="A117" s="15"/>
+      <c r="B117" s="12"/>
+      <c r="C117" s="12"/>
+      <c r="D117" s="10"/>
+      <c r="E117" s="16"/>
+      <c r="F117" s="10"/>
+      <c r="G117" s="16"/>
       <c r="H117" s="17"/>
       <c r="I117" s="4"/>
       <c r="J117" s="4"/>
@@ -5210,27 +3280,13 @@
       <c r="Z117" s="4"/>
     </row>
     <row r="118" spans="1:26">
-      <c r="A118" s="11">
-        <v>46098</v>
-      </c>
-      <c r="B118" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C118" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="D118" s="7">
-        <v>18.28</v>
-      </c>
-      <c r="E118" s="7">
-        <v>1.28</v>
-      </c>
-      <c r="F118" s="7">
-        <v>19.559999999999999</v>
-      </c>
-      <c r="G118" s="7">
-        <v>3.29</v>
-      </c>
+      <c r="A118" s="11"/>
+      <c r="B118" s="6"/>
+      <c r="C118" s="6"/>
+      <c r="D118" s="7"/>
+      <c r="E118" s="7"/>
+      <c r="F118" s="7"/>
+      <c r="G118" s="7"/>
       <c r="H118" s="6"/>
       <c r="I118" s="4"/>
       <c r="J118" s="4"/>
@@ -5252,27 +3308,13 @@
       <c r="Z118" s="4"/>
     </row>
     <row r="119" spans="1:26">
-      <c r="A119" s="5">
-        <v>46099</v>
-      </c>
-      <c r="B119" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C119" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="D119" s="7">
-        <v>45.47</v>
-      </c>
-      <c r="E119" s="7">
-        <v>0.91</v>
-      </c>
-      <c r="F119" s="7">
-        <v>46.38</v>
-      </c>
-      <c r="G119" s="7">
-        <v>0</v>
-      </c>
+      <c r="A119" s="5"/>
+      <c r="B119" s="6"/>
+      <c r="C119" s="6"/>
+      <c r="D119" s="7"/>
+      <c r="E119" s="7"/>
+      <c r="F119" s="7"/>
+      <c r="G119" s="7"/>
       <c r="H119" s="6"/>
       <c r="I119" s="4"/>
       <c r="J119" s="4"/>
@@ -5294,27 +3336,13 @@
       <c r="Z119" s="4"/>
     </row>
     <row r="120" spans="1:26">
-      <c r="A120" s="5">
-        <v>46099</v>
-      </c>
-      <c r="B120" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C120" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="D120" s="7">
-        <v>45.47</v>
-      </c>
-      <c r="E120" s="7">
-        <v>0.91</v>
-      </c>
-      <c r="F120" s="7">
-        <v>46.38</v>
-      </c>
-      <c r="G120" s="7">
-        <v>0</v>
-      </c>
+      <c r="A120" s="5"/>
+      <c r="B120" s="6"/>
+      <c r="C120" s="6"/>
+      <c r="D120" s="7"/>
+      <c r="E120" s="7"/>
+      <c r="F120" s="7"/>
+      <c r="G120" s="7"/>
       <c r="H120" s="6"/>
       <c r="I120" s="4"/>
       <c r="J120" s="4"/>
@@ -5336,27 +3364,13 @@
       <c r="Z120" s="4"/>
     </row>
     <row r="121" spans="1:26">
-      <c r="A121" s="18">
-        <v>46100</v>
-      </c>
-      <c r="B121" s="12" t="s">
-        <v>51</v>
-      </c>
-      <c r="C121" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="D121" s="14">
-        <v>91.4</v>
-      </c>
-      <c r="E121" s="16">
-        <v>0</v>
-      </c>
-      <c r="F121" s="14">
-        <v>91.4</v>
-      </c>
-      <c r="G121" s="16">
-        <v>0</v>
-      </c>
+      <c r="A121" s="18"/>
+      <c r="B121" s="12"/>
+      <c r="C121" s="12"/>
+      <c r="D121" s="14"/>
+      <c r="E121" s="16"/>
+      <c r="F121" s="14"/>
+      <c r="G121" s="16"/>
       <c r="H121" s="17"/>
       <c r="I121" s="4"/>
       <c r="J121" s="4"/>
@@ -5378,27 +3392,13 @@
       <c r="Z121" s="4"/>
     </row>
     <row r="122" spans="1:26">
-      <c r="A122" s="11">
-        <v>46101</v>
-      </c>
-      <c r="B122" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C122" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="D122" s="7">
-        <v>22.28</v>
-      </c>
-      <c r="E122" s="7">
-        <v>1.56</v>
-      </c>
-      <c r="F122" s="7">
-        <v>29.08</v>
-      </c>
-      <c r="G122" s="7">
-        <v>5.24</v>
-      </c>
+      <c r="A122" s="11"/>
+      <c r="B122" s="6"/>
+      <c r="C122" s="6"/>
+      <c r="D122" s="7"/>
+      <c r="E122" s="7"/>
+      <c r="F122" s="7"/>
+      <c r="G122" s="7"/>
       <c r="H122" s="6"/>
       <c r="I122" s="4"/>
       <c r="J122" s="4"/>
@@ -5420,27 +3420,13 @@
       <c r="Z122" s="4"/>
     </row>
     <row r="123" spans="1:26">
-      <c r="A123" s="11">
-        <v>46101</v>
-      </c>
-      <c r="B123" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C123" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="D123" s="7">
-        <v>6.25</v>
-      </c>
-      <c r="E123" s="7">
-        <v>0.44</v>
-      </c>
-      <c r="F123" s="7">
-        <v>7.69</v>
-      </c>
-      <c r="G123" s="7">
-        <v>1</v>
-      </c>
+      <c r="A123" s="11"/>
+      <c r="B123" s="6"/>
+      <c r="C123" s="6"/>
+      <c r="D123" s="7"/>
+      <c r="E123" s="7"/>
+      <c r="F123" s="7"/>
+      <c r="G123" s="7"/>
       <c r="H123" s="6"/>
       <c r="I123" s="4"/>
       <c r="J123" s="4"/>
@@ -5462,27 +3448,13 @@
       <c r="Z123" s="4"/>
     </row>
     <row r="124" spans="1:26">
-      <c r="A124" s="5">
-        <v>46101</v>
-      </c>
-      <c r="B124" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C124" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="D124" s="7">
-        <v>16.489999999999998</v>
-      </c>
-      <c r="E124" s="7">
-        <v>1.1499999999999999</v>
-      </c>
-      <c r="F124" s="7">
-        <v>22</v>
-      </c>
-      <c r="G124" s="7">
-        <v>4.3600000000000003</v>
-      </c>
+      <c r="A124" s="5"/>
+      <c r="B124" s="6"/>
+      <c r="C124" s="6"/>
+      <c r="D124" s="7"/>
+      <c r="E124" s="7"/>
+      <c r="F124" s="7"/>
+      <c r="G124" s="7"/>
       <c r="H124" s="6"/>
       <c r="I124" s="4"/>
       <c r="J124" s="4"/>
@@ -5504,27 +3476,13 @@
       <c r="Z124" s="4"/>
     </row>
     <row r="125" spans="1:26">
-      <c r="A125" s="5">
-        <v>46102</v>
-      </c>
-      <c r="B125" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C125" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="D125" s="7">
-        <v>23.77</v>
-      </c>
-      <c r="E125" s="7">
-        <v>1.66</v>
-      </c>
-      <c r="F125" s="7">
-        <v>25.43</v>
-      </c>
-      <c r="G125" s="7">
-        <v>5.22</v>
-      </c>
+      <c r="A125" s="5"/>
+      <c r="B125" s="6"/>
+      <c r="C125" s="6"/>
+      <c r="D125" s="7"/>
+      <c r="E125" s="7"/>
+      <c r="F125" s="7"/>
+      <c r="G125" s="7"/>
       <c r="H125" s="6"/>
       <c r="I125" s="4"/>
       <c r="J125" s="4"/>
@@ -5546,27 +3504,13 @@
       <c r="Z125" s="4"/>
     </row>
     <row r="126" spans="1:26">
-      <c r="A126" s="5">
-        <v>46102</v>
-      </c>
-      <c r="B126" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="C126" s="6" t="s">
-        <v>95</v>
-      </c>
-      <c r="D126" s="7">
-        <v>16.04</v>
-      </c>
-      <c r="E126" s="7">
-        <v>0</v>
-      </c>
-      <c r="F126" s="7">
-        <v>16.04</v>
-      </c>
-      <c r="G126" s="7">
-        <v>0</v>
-      </c>
+      <c r="A126" s="5"/>
+      <c r="B126" s="6"/>
+      <c r="C126" s="6"/>
+      <c r="D126" s="7"/>
+      <c r="E126" s="7"/>
+      <c r="F126" s="7"/>
+      <c r="G126" s="7"/>
       <c r="H126" s="6"/>
       <c r="I126" s="4"/>
       <c r="J126" s="4"/>
@@ -5588,27 +3532,13 @@
       <c r="Z126" s="4"/>
     </row>
     <row r="127" spans="1:26">
-      <c r="A127" s="15">
-        <v>46102</v>
-      </c>
-      <c r="B127" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="C127" s="12" t="s">
-        <v>50</v>
-      </c>
-      <c r="D127" s="16">
-        <v>82.79</v>
-      </c>
-      <c r="E127" s="16">
-        <v>0</v>
-      </c>
-      <c r="F127" s="16">
-        <v>82.79</v>
-      </c>
-      <c r="G127" s="16">
-        <v>0</v>
-      </c>
+      <c r="A127" s="15"/>
+      <c r="B127" s="12"/>
+      <c r="C127" s="12"/>
+      <c r="D127" s="16"/>
+      <c r="E127" s="16"/>
+      <c r="F127" s="16"/>
+      <c r="G127" s="16"/>
       <c r="H127" s="17"/>
       <c r="I127" s="4"/>
       <c r="J127" s="4"/>
@@ -5630,50 +3560,22 @@
       <c r="Z127" s="4"/>
     </row>
     <row r="128" spans="1:26">
-      <c r="A128" s="19">
-        <v>46103</v>
-      </c>
-      <c r="B128" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C128" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="D128" s="10">
-        <v>12.5</v>
-      </c>
-      <c r="E128" s="10">
-        <v>0.88</v>
-      </c>
-      <c r="F128" s="10">
-        <v>14.38</v>
-      </c>
-      <c r="G128" s="10">
-        <v>1</v>
-      </c>
+      <c r="A128" s="19"/>
+      <c r="B128" s="6"/>
+      <c r="C128" s="6"/>
+      <c r="D128" s="10"/>
+      <c r="E128" s="10"/>
+      <c r="F128" s="10"/>
+      <c r="G128" s="10"/>
     </row>
     <row r="129" spans="1:26">
-      <c r="A129" s="15">
-        <v>46103</v>
-      </c>
-      <c r="B129" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="C129" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="D129" s="16">
-        <v>103.66</v>
-      </c>
-      <c r="E129" s="16">
-        <v>0</v>
-      </c>
-      <c r="F129" s="16">
-        <v>103.66</v>
-      </c>
-      <c r="G129" s="16">
-        <v>0</v>
-      </c>
+      <c r="A129" s="15"/>
+      <c r="B129" s="12"/>
+      <c r="C129" s="12"/>
+      <c r="D129" s="16"/>
+      <c r="E129" s="16"/>
+      <c r="F129" s="16"/>
+      <c r="G129" s="16"/>
       <c r="H129" s="17"/>
       <c r="I129" s="4"/>
       <c r="J129" s="4"/>
@@ -5695,27 +3597,13 @@
       <c r="Z129" s="4"/>
     </row>
     <row r="130" spans="1:26">
-      <c r="A130" s="11">
-        <v>46103</v>
-      </c>
-      <c r="B130" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="C130" s="21" t="s">
-        <v>96</v>
-      </c>
-      <c r="D130" s="14">
-        <v>14.99</v>
-      </c>
-      <c r="E130" s="16">
-        <v>0</v>
-      </c>
-      <c r="F130" s="14">
-        <v>14.99</v>
-      </c>
-      <c r="G130" s="16">
-        <v>0</v>
-      </c>
+      <c r="A130" s="11"/>
+      <c r="B130" s="12"/>
+      <c r="C130" s="21"/>
+      <c r="D130" s="14"/>
+      <c r="E130" s="16"/>
+      <c r="F130" s="14"/>
+      <c r="G130" s="16"/>
       <c r="H130" s="6"/>
       <c r="I130" s="4"/>
       <c r="J130" s="4"/>
@@ -5737,27 +3625,13 @@
       <c r="Z130" s="4"/>
     </row>
     <row r="131" spans="1:26">
-      <c r="A131" s="5">
-        <v>46104</v>
-      </c>
-      <c r="B131" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C131" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="D131" s="7">
-        <v>17.98</v>
-      </c>
-      <c r="E131" s="7">
-        <v>1.26</v>
-      </c>
-      <c r="F131" s="7">
-        <v>19.239999999999998</v>
-      </c>
-      <c r="G131" s="7">
-        <v>3.59</v>
-      </c>
+      <c r="A131" s="5"/>
+      <c r="B131" s="6"/>
+      <c r="C131" s="6"/>
+      <c r="D131" s="7"/>
+      <c r="E131" s="7"/>
+      <c r="F131" s="7"/>
+      <c r="G131" s="7"/>
       <c r="H131" s="6"/>
       <c r="I131" s="4"/>
       <c r="J131" s="4"/>
@@ -5779,50 +3653,22 @@
       <c r="Z131" s="4"/>
     </row>
     <row r="132" spans="1:26">
-      <c r="A132" s="19">
-        <v>46104</v>
-      </c>
-      <c r="B132" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C132" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="D132" s="10">
-        <v>3.95</v>
-      </c>
-      <c r="E132" s="10">
-        <v>0.28000000000000003</v>
-      </c>
-      <c r="F132" s="10">
-        <v>5.23</v>
-      </c>
-      <c r="G132" s="10">
-        <v>1</v>
-      </c>
+      <c r="A132" s="19"/>
+      <c r="B132" s="6"/>
+      <c r="C132" s="6"/>
+      <c r="D132" s="10"/>
+      <c r="E132" s="10"/>
+      <c r="F132" s="10"/>
+      <c r="G132" s="10"/>
     </row>
     <row r="133" spans="1:26">
-      <c r="A133" s="5">
-        <v>46105</v>
-      </c>
-      <c r="B133" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C133" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="D133" s="7">
-        <v>6.39</v>
-      </c>
-      <c r="E133" s="7">
-        <v>0.25</v>
-      </c>
-      <c r="F133" s="7">
-        <v>6.64</v>
-      </c>
-      <c r="G133" s="7">
-        <v>0</v>
-      </c>
+      <c r="A133" s="5"/>
+      <c r="B133" s="6"/>
+      <c r="C133" s="6"/>
+      <c r="D133" s="7"/>
+      <c r="E133" s="7"/>
+      <c r="F133" s="7"/>
+      <c r="G133" s="7"/>
       <c r="H133" s="6"/>
       <c r="I133" s="4"/>
       <c r="J133" s="4"/>
@@ -5844,27 +3690,13 @@
       <c r="Z133" s="4"/>
     </row>
     <row r="134" spans="1:26">
-      <c r="A134" s="5">
-        <v>46105</v>
-      </c>
-      <c r="B134" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C134" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="D134" s="7">
-        <v>46.93</v>
-      </c>
-      <c r="E134" s="7">
-        <v>1.43</v>
-      </c>
-      <c r="F134" s="7">
-        <v>48.36</v>
-      </c>
-      <c r="G134" s="7">
-        <v>0</v>
-      </c>
+      <c r="A134" s="5"/>
+      <c r="B134" s="6"/>
+      <c r="C134" s="6"/>
+      <c r="D134" s="7"/>
+      <c r="E134" s="7"/>
+      <c r="F134" s="7"/>
+      <c r="G134" s="7"/>
       <c r="H134" s="6"/>
       <c r="I134" s="4"/>
       <c r="J134" s="4"/>
@@ -5886,27 +3718,13 @@
       <c r="Z134" s="4"/>
     </row>
     <row r="135" spans="1:26">
-      <c r="A135" s="11">
-        <v>46107</v>
-      </c>
-      <c r="B135" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C135" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="D135" s="7">
-        <v>18.18</v>
-      </c>
-      <c r="E135" s="7">
-        <v>1.27</v>
-      </c>
-      <c r="F135" s="7">
-        <v>19.45</v>
-      </c>
-      <c r="G135" s="7">
-        <v>0</v>
-      </c>
+      <c r="A135" s="11"/>
+      <c r="B135" s="6"/>
+      <c r="C135" s="6"/>
+      <c r="D135" s="7"/>
+      <c r="E135" s="7"/>
+      <c r="F135" s="7"/>
+      <c r="G135" s="7"/>
       <c r="H135" s="6"/>
       <c r="I135" s="4"/>
       <c r="J135" s="4"/>
@@ -5928,27 +3746,13 @@
       <c r="Z135" s="4"/>
     </row>
     <row r="136" spans="1:26">
-      <c r="A136" s="5">
-        <v>46107</v>
-      </c>
-      <c r="B136" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C136" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="D136" s="7">
-        <v>13.67</v>
-      </c>
-      <c r="E136" s="7">
-        <v>0</v>
-      </c>
-      <c r="F136" s="7">
-        <v>12.59</v>
-      </c>
-      <c r="G136" s="7">
-        <v>0</v>
-      </c>
+      <c r="A136" s="5"/>
+      <c r="B136" s="6"/>
+      <c r="C136" s="6"/>
+      <c r="D136" s="7"/>
+      <c r="E136" s="7"/>
+      <c r="F136" s="7"/>
+      <c r="G136" s="7"/>
       <c r="H136" s="6"/>
       <c r="I136" s="4"/>
       <c r="J136" s="4"/>
@@ -5970,27 +3774,13 @@
       <c r="Z136" s="4"/>
     </row>
     <row r="137" spans="1:26">
-      <c r="A137" s="11">
-        <v>46108</v>
-      </c>
-      <c r="B137" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C137" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="D137" s="7">
-        <v>67</v>
-      </c>
-      <c r="E137" s="7">
-        <v>1.31</v>
-      </c>
-      <c r="F137" s="7">
-        <v>68.31</v>
-      </c>
-      <c r="G137" s="7">
-        <v>0</v>
-      </c>
+      <c r="A137" s="11"/>
+      <c r="B137" s="6"/>
+      <c r="C137" s="6"/>
+      <c r="D137" s="7"/>
+      <c r="E137" s="7"/>
+      <c r="F137" s="7"/>
+      <c r="G137" s="7"/>
       <c r="H137" s="6"/>
       <c r="I137" s="4"/>
       <c r="J137" s="4"/>
@@ -6012,50 +3802,22 @@
       <c r="Z137" s="4"/>
     </row>
     <row r="138" spans="1:26">
-      <c r="A138" s="19">
-        <v>46108</v>
-      </c>
-      <c r="B138" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C138" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="D138" s="10">
-        <v>21.57</v>
-      </c>
-      <c r="E138" s="10">
-        <v>1.51</v>
-      </c>
-      <c r="F138" s="10">
-        <v>23.08</v>
-      </c>
-      <c r="G138" s="10">
-        <v>5</v>
-      </c>
+      <c r="A138" s="19"/>
+      <c r="B138" s="6"/>
+      <c r="C138" s="6"/>
+      <c r="D138" s="10"/>
+      <c r="E138" s="10"/>
+      <c r="F138" s="10"/>
+      <c r="G138" s="10"/>
     </row>
     <row r="139" spans="1:26">
-      <c r="A139" s="5">
-        <v>46108</v>
-      </c>
-      <c r="B139" s="12" t="s">
-        <v>63</v>
-      </c>
-      <c r="C139" s="12" t="s">
-        <v>61</v>
-      </c>
-      <c r="D139" s="14">
-        <v>382.8</v>
-      </c>
-      <c r="E139" s="16">
-        <v>0</v>
-      </c>
-      <c r="F139" s="14">
-        <v>382.8</v>
-      </c>
-      <c r="G139" s="16">
-        <v>0</v>
-      </c>
+      <c r="A139" s="5"/>
+      <c r="B139" s="12"/>
+      <c r="C139" s="12"/>
+      <c r="D139" s="14"/>
+      <c r="E139" s="16"/>
+      <c r="F139" s="14"/>
+      <c r="G139" s="16"/>
       <c r="H139" s="6"/>
       <c r="I139" s="4"/>
       <c r="J139" s="4"/>
@@ -6077,27 +3839,13 @@
       <c r="Z139" s="4"/>
     </row>
     <row r="140" spans="1:26">
-      <c r="A140" s="15">
-        <v>46110</v>
-      </c>
-      <c r="B140" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="C140" s="12" t="s">
-        <v>83</v>
-      </c>
-      <c r="D140" s="16">
-        <v>841.61</v>
-      </c>
-      <c r="E140" s="16">
-        <v>113.62</v>
-      </c>
-      <c r="F140" s="16">
-        <v>955.23</v>
-      </c>
-      <c r="G140" s="16">
-        <v>0</v>
-      </c>
+      <c r="A140" s="15"/>
+      <c r="B140" s="6"/>
+      <c r="C140" s="12"/>
+      <c r="D140" s="16"/>
+      <c r="E140" s="16"/>
+      <c r="F140" s="16"/>
+      <c r="G140" s="16"/>
       <c r="H140" s="17"/>
       <c r="I140" s="4"/>
       <c r="J140" s="4"/>
@@ -6119,27 +3867,13 @@
       <c r="Z140" s="4"/>
     </row>
     <row r="141" spans="1:26">
-      <c r="A141" s="11">
-        <v>46110</v>
-      </c>
-      <c r="B141" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="C141" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="D141" s="7">
-        <v>82.79</v>
-      </c>
-      <c r="E141" s="7">
-        <v>4.8099999999999996</v>
-      </c>
-      <c r="F141" s="7">
-        <v>82.79</v>
-      </c>
-      <c r="G141" s="7">
-        <v>0</v>
-      </c>
+      <c r="A141" s="11"/>
+      <c r="B141" s="6"/>
+      <c r="C141" s="6"/>
+      <c r="D141" s="7"/>
+      <c r="E141" s="7"/>
+      <c r="F141" s="7"/>
+      <c r="G141" s="7"/>
       <c r="H141" s="6"/>
       <c r="I141" s="4"/>
       <c r="J141" s="4"/>
@@ -6161,27 +3895,13 @@
       <c r="Z141" s="4"/>
     </row>
     <row r="142" spans="1:26">
-      <c r="A142" s="11">
-        <v>46110</v>
-      </c>
-      <c r="B142" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C142" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="D142" s="7">
-        <v>23.38</v>
-      </c>
-      <c r="E142" s="7">
-        <v>1.64</v>
-      </c>
-      <c r="F142" s="7">
-        <v>30.52</v>
-      </c>
-      <c r="G142" s="7">
-        <v>5.5</v>
-      </c>
+      <c r="A142" s="11"/>
+      <c r="B142" s="6"/>
+      <c r="C142" s="6"/>
+      <c r="D142" s="7"/>
+      <c r="E142" s="7"/>
+      <c r="F142" s="7"/>
+      <c r="G142" s="7"/>
       <c r="H142" s="6"/>
       <c r="I142" s="4"/>
       <c r="J142" s="4"/>
@@ -6203,27 +3923,13 @@
       <c r="Z142" s="4"/>
     </row>
     <row r="143" spans="1:26">
-      <c r="A143" s="11">
-        <v>46110</v>
-      </c>
-      <c r="B143" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C143" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="D143" s="7">
-        <v>59.76</v>
-      </c>
-      <c r="E143" s="7">
-        <v>0.32</v>
-      </c>
-      <c r="F143" s="7">
-        <v>60.08</v>
-      </c>
-      <c r="G143" s="7">
-        <v>0</v>
-      </c>
+      <c r="A143" s="11"/>
+      <c r="B143" s="6"/>
+      <c r="C143" s="6"/>
+      <c r="D143" s="7"/>
+      <c r="E143" s="7"/>
+      <c r="F143" s="7"/>
+      <c r="G143" s="7"/>
       <c r="H143" s="6"/>
       <c r="I143" s="4"/>
       <c r="J143" s="4"/>
@@ -6245,27 +3951,13 @@
       <c r="Z143" s="4"/>
     </row>
     <row r="144" spans="1:26">
-      <c r="A144" s="11">
-        <v>46111</v>
-      </c>
-      <c r="B144" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C144" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="D144" s="7">
-        <v>33.99</v>
-      </c>
-      <c r="E144" s="7">
-        <v>2.5499999999999998</v>
-      </c>
-      <c r="F144" s="7">
-        <v>44.44</v>
-      </c>
-      <c r="G144" s="7">
-        <v>7.9</v>
-      </c>
+      <c r="A144" s="11"/>
+      <c r="B144" s="6"/>
+      <c r="C144" s="6"/>
+      <c r="D144" s="7"/>
+      <c r="E144" s="7"/>
+      <c r="F144" s="7"/>
+      <c r="G144" s="7"/>
       <c r="H144" s="6"/>
       <c r="I144" s="4"/>
       <c r="J144" s="4"/>
@@ -6287,27 +3979,13 @@
       <c r="Z144" s="4"/>
     </row>
     <row r="145" spans="1:26">
-      <c r="A145" s="11">
-        <v>46114</v>
-      </c>
-      <c r="B145" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C145" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="D145" s="7">
-        <v>34.47</v>
-      </c>
-      <c r="E145" s="7">
-        <v>1.1200000000000001</v>
-      </c>
-      <c r="F145" s="7">
-        <v>35.590000000000003</v>
-      </c>
-      <c r="G145" s="7">
-        <v>0</v>
-      </c>
+      <c r="A145" s="11"/>
+      <c r="B145" s="6"/>
+      <c r="C145" s="6"/>
+      <c r="D145" s="7"/>
+      <c r="E145" s="7"/>
+      <c r="F145" s="7"/>
+      <c r="G145" s="7"/>
       <c r="H145" s="6"/>
       <c r="I145" s="4"/>
       <c r="J145" s="4"/>
@@ -6329,27 +4007,13 @@
       <c r="Z145" s="4"/>
     </row>
     <row r="146" spans="1:26">
-      <c r="A146" s="11">
-        <v>46114</v>
-      </c>
-      <c r="B146" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C146" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="D146" s="7">
-        <v>16.670000000000002</v>
-      </c>
-      <c r="E146" s="7">
-        <v>1.25</v>
-      </c>
-      <c r="F146" s="7">
-        <v>20.92</v>
-      </c>
-      <c r="G146" s="7">
-        <v>3</v>
-      </c>
+      <c r="A146" s="11"/>
+      <c r="B146" s="6"/>
+      <c r="C146" s="6"/>
+      <c r="D146" s="7"/>
+      <c r="E146" s="7"/>
+      <c r="F146" s="7"/>
+      <c r="G146" s="7"/>
       <c r="H146" s="6"/>
       <c r="I146" s="4"/>
       <c r="J146" s="4"/>
@@ -6371,27 +4035,13 @@
       <c r="Z146" s="4"/>
     </row>
     <row r="147" spans="1:26">
-      <c r="A147" s="11">
-        <v>46114</v>
-      </c>
-      <c r="B147" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="C147" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="D147" s="14">
-        <v>28.29</v>
-      </c>
-      <c r="E147" s="7">
-        <v>0</v>
-      </c>
-      <c r="F147" s="14">
-        <v>28.29</v>
-      </c>
-      <c r="G147" s="7">
-        <v>0</v>
-      </c>
+      <c r="A147" s="11"/>
+      <c r="B147" s="12"/>
+      <c r="C147" s="13"/>
+      <c r="D147" s="14"/>
+      <c r="E147" s="7"/>
+      <c r="F147" s="14"/>
+      <c r="G147" s="7"/>
       <c r="H147" s="6"/>
       <c r="I147" s="4"/>
       <c r="J147" s="4"/>
@@ -6413,27 +4063,13 @@
       <c r="Z147" s="4"/>
     </row>
     <row r="148" spans="1:26">
-      <c r="A148" s="11">
-        <v>46116</v>
-      </c>
-      <c r="B148" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="C148" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="D148" s="14">
-        <v>36</v>
-      </c>
-      <c r="E148" s="7">
-        <v>0</v>
-      </c>
-      <c r="F148" s="14">
-        <v>36</v>
-      </c>
-      <c r="G148" s="7">
-        <v>0</v>
-      </c>
+      <c r="A148" s="11"/>
+      <c r="B148" s="6"/>
+      <c r="C148" s="6"/>
+      <c r="D148" s="14"/>
+      <c r="E148" s="7"/>
+      <c r="F148" s="14"/>
+      <c r="G148" s="7"/>
       <c r="H148" s="6"/>
       <c r="I148" s="4"/>
       <c r="J148" s="4"/>
@@ -6455,27 +4091,13 @@
       <c r="Z148" s="4"/>
     </row>
     <row r="149" spans="1:26">
-      <c r="A149" s="15">
-        <v>46120</v>
-      </c>
-      <c r="B149" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="C149" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="D149" s="16">
-        <v>275.47000000000003</v>
-      </c>
-      <c r="E149" s="16">
-        <v>0</v>
-      </c>
-      <c r="F149" s="16">
-        <v>275.47000000000003</v>
-      </c>
-      <c r="G149" s="16">
-        <v>0</v>
-      </c>
+      <c r="A149" s="15"/>
+      <c r="B149" s="12"/>
+      <c r="C149" s="12"/>
+      <c r="D149" s="16"/>
+      <c r="E149" s="16"/>
+      <c r="F149" s="16"/>
+      <c r="G149" s="16"/>
       <c r="H149" s="17"/>
       <c r="I149" s="4"/>
       <c r="J149" s="4"/>
@@ -6497,27 +4119,13 @@
       <c r="Z149" s="4"/>
     </row>
     <row r="150" spans="1:26">
-      <c r="A150" s="11">
-        <v>46122</v>
-      </c>
-      <c r="B150" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="C150" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="D150" s="10">
-        <v>886.7</v>
-      </c>
-      <c r="E150" s="7">
-        <v>0</v>
-      </c>
-      <c r="F150" s="10">
-        <v>886.7</v>
-      </c>
-      <c r="G150" s="7">
-        <v>0</v>
-      </c>
+      <c r="A150" s="11"/>
+      <c r="B150" s="6"/>
+      <c r="C150" s="6"/>
+      <c r="D150" s="10"/>
+      <c r="E150" s="7"/>
+      <c r="F150" s="10"/>
+      <c r="G150" s="7"/>
       <c r="H150" s="6"/>
       <c r="I150" s="12"/>
       <c r="J150" s="4"/>
@@ -6539,27 +4147,13 @@
       <c r="Z150" s="4"/>
     </row>
     <row r="151" spans="1:26">
-      <c r="A151" s="15">
-        <v>46122</v>
-      </c>
-      <c r="B151" s="12" t="s">
-        <v>56</v>
-      </c>
-      <c r="C151" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="D151" s="20">
-        <v>1250</v>
-      </c>
-      <c r="E151" s="16">
-        <v>0</v>
-      </c>
-      <c r="F151" s="20">
-        <v>1250</v>
-      </c>
-      <c r="G151" s="16">
-        <v>0</v>
-      </c>
+      <c r="A151" s="15"/>
+      <c r="B151" s="12"/>
+      <c r="C151" s="12"/>
+      <c r="D151" s="20"/>
+      <c r="E151" s="16"/>
+      <c r="F151" s="20"/>
+      <c r="G151" s="16"/>
       <c r="H151" s="17"/>
       <c r="I151" s="4"/>
       <c r="J151" s="4"/>
@@ -6581,27 +4175,13 @@
       <c r="Z151" s="4"/>
     </row>
     <row r="152" spans="1:26">
-      <c r="A152" s="15">
-        <v>46123</v>
-      </c>
-      <c r="B152" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C152" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="D152" s="7">
-        <v>33.369999999999997</v>
-      </c>
-      <c r="E152" s="7">
-        <v>2.5</v>
-      </c>
-      <c r="F152" s="7">
-        <v>42.33</v>
-      </c>
-      <c r="G152" s="7">
-        <v>6.46</v>
-      </c>
+      <c r="A152" s="15"/>
+      <c r="B152" s="6"/>
+      <c r="C152" s="6"/>
+      <c r="D152" s="7"/>
+      <c r="E152" s="7"/>
+      <c r="F152" s="7"/>
+      <c r="G152" s="7"/>
       <c r="H152" s="6"/>
       <c r="I152" s="4"/>
       <c r="J152" s="4"/>
@@ -6623,27 +4203,13 @@
       <c r="Z152" s="4"/>
     </row>
     <row r="153" spans="1:26">
-      <c r="A153" s="11">
-        <v>46124</v>
-      </c>
-      <c r="B153" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="C153" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="D153" s="7">
-        <v>414.61</v>
-      </c>
-      <c r="E153" s="7">
-        <v>0</v>
-      </c>
-      <c r="F153" s="7">
-        <v>414.61</v>
-      </c>
-      <c r="G153" s="7">
-        <v>0</v>
-      </c>
+      <c r="A153" s="11"/>
+      <c r="B153" s="6"/>
+      <c r="C153" s="6"/>
+      <c r="D153" s="7"/>
+      <c r="E153" s="7"/>
+      <c r="F153" s="7"/>
+      <c r="G153" s="7"/>
       <c r="H153" s="6"/>
       <c r="I153" s="4"/>
       <c r="J153" s="4"/>
@@ -6665,73 +4231,31 @@
       <c r="Z153" s="4"/>
     </row>
     <row r="154" spans="1:26">
-      <c r="A154" s="19">
-        <v>46124</v>
-      </c>
-      <c r="B154" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C154" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="D154" s="10">
-        <v>123.67</v>
-      </c>
-      <c r="E154" s="10">
-        <v>9.67</v>
-      </c>
-      <c r="F154" s="10">
-        <v>124.34</v>
-      </c>
-      <c r="G154" s="10">
-        <v>0</v>
-      </c>
+      <c r="A154" s="19"/>
+      <c r="B154" s="6"/>
+      <c r="C154" s="6"/>
+      <c r="D154" s="10"/>
+      <c r="E154" s="10"/>
+      <c r="F154" s="10"/>
+      <c r="G154" s="10"/>
     </row>
     <row r="155" spans="1:26">
-      <c r="A155" s="19">
-        <v>46126</v>
-      </c>
-      <c r="B155" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C155" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="D155" s="10">
-        <v>40.130000000000003</v>
-      </c>
-      <c r="E155" s="10">
-        <v>0.93</v>
-      </c>
-      <c r="F155" s="10">
-        <v>41.06</v>
-      </c>
-      <c r="G155" s="10">
-        <v>0</v>
-      </c>
+      <c r="A155" s="19"/>
+      <c r="B155" s="6"/>
+      <c r="C155" s="6"/>
+      <c r="D155" s="10"/>
+      <c r="E155" s="10"/>
+      <c r="F155" s="10"/>
+      <c r="G155" s="10"/>
     </row>
     <row r="156" spans="1:26">
-      <c r="A156" s="19">
-        <v>46126</v>
-      </c>
-      <c r="B156" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="C156" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="D156" s="16">
-        <v>101</v>
-      </c>
-      <c r="E156" s="16">
-        <v>0</v>
-      </c>
-      <c r="F156" s="16">
-        <v>101</v>
-      </c>
-      <c r="G156" s="16">
-        <v>0</v>
-      </c>
+      <c r="A156" s="19"/>
+      <c r="B156" s="12"/>
+      <c r="C156" s="12"/>
+      <c r="D156" s="16"/>
+      <c r="E156" s="16"/>
+      <c r="F156" s="16"/>
+      <c r="G156" s="16"/>
       <c r="H156" s="17"/>
       <c r="I156" s="4"/>
       <c r="J156" s="4"/>
@@ -6753,27 +4277,13 @@
       <c r="Z156" s="4"/>
     </row>
     <row r="157" spans="1:26">
-      <c r="A157" s="11">
-        <v>46126</v>
-      </c>
-      <c r="B157" s="12" t="s">
-        <v>102</v>
-      </c>
-      <c r="C157" s="12" t="s">
-        <v>103</v>
-      </c>
-      <c r="D157" s="10">
-        <v>295</v>
-      </c>
-      <c r="E157" s="7">
-        <v>0</v>
-      </c>
-      <c r="F157" s="7">
-        <v>295</v>
-      </c>
-      <c r="G157" s="10">
-        <v>0</v>
-      </c>
+      <c r="A157" s="11"/>
+      <c r="B157" s="12"/>
+      <c r="C157" s="12"/>
+      <c r="D157" s="10"/>
+      <c r="E157" s="7"/>
+      <c r="F157" s="7"/>
+      <c r="G157" s="10"/>
       <c r="H157" s="17"/>
       <c r="I157" s="4"/>
       <c r="J157" s="4"/>
@@ -6795,27 +4305,13 @@
       <c r="Z157" s="4"/>
     </row>
     <row r="158" spans="1:26">
-      <c r="A158" s="15">
-        <v>46127</v>
-      </c>
-      <c r="B158" s="12" t="s">
-        <v>56</v>
-      </c>
-      <c r="C158" s="12" t="s">
-        <v>57</v>
-      </c>
-      <c r="D158" s="10">
-        <v>500</v>
-      </c>
-      <c r="E158" s="16">
-        <v>0</v>
-      </c>
-      <c r="F158" s="10">
-        <v>500</v>
-      </c>
-      <c r="G158" s="16">
-        <v>0</v>
-      </c>
+      <c r="A158" s="15"/>
+      <c r="B158" s="12"/>
+      <c r="C158" s="12"/>
+      <c r="D158" s="10"/>
+      <c r="E158" s="16"/>
+      <c r="F158" s="10"/>
+      <c r="G158" s="16"/>
       <c r="H158" s="17"/>
       <c r="I158" s="4"/>
       <c r="J158" s="4"/>
@@ -6837,27 +4333,13 @@
       <c r="Z158" s="4"/>
     </row>
     <row r="159" spans="1:26">
-      <c r="A159" s="15">
-        <v>46129</v>
-      </c>
-      <c r="B159" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="C159" s="12" t="s">
-        <v>47</v>
-      </c>
-      <c r="D159" s="14">
-        <v>28.28</v>
-      </c>
-      <c r="E159" s="16">
-        <v>0</v>
-      </c>
-      <c r="F159" s="14">
-        <v>28.28</v>
-      </c>
-      <c r="G159" s="16">
-        <v>0</v>
-      </c>
+      <c r="A159" s="15"/>
+      <c r="B159" s="12"/>
+      <c r="C159" s="12"/>
+      <c r="D159" s="14"/>
+      <c r="E159" s="16"/>
+      <c r="F159" s="14"/>
+      <c r="G159" s="16"/>
       <c r="H159" s="17"/>
       <c r="I159" s="4"/>
       <c r="J159" s="4"/>
@@ -6879,27 +4361,13 @@
       <c r="Z159" s="4"/>
     </row>
     <row r="160" spans="1:26">
-      <c r="A160" s="15">
-        <v>46130</v>
-      </c>
-      <c r="B160" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C160" s="6" t="s">
-        <v>104</v>
-      </c>
-      <c r="D160" s="7">
-        <v>49.99</v>
-      </c>
-      <c r="E160" s="7">
-        <v>5.36</v>
-      </c>
-      <c r="F160" s="7">
-        <v>65.02</v>
-      </c>
-      <c r="G160" s="7">
-        <v>9.67</v>
-      </c>
+      <c r="A160" s="15"/>
+      <c r="B160" s="6"/>
+      <c r="C160" s="6"/>
+      <c r="D160" s="7"/>
+      <c r="E160" s="7"/>
+      <c r="F160" s="7"/>
+      <c r="G160" s="7"/>
       <c r="H160" s="6"/>
       <c r="I160" s="4"/>
       <c r="J160" s="4"/>
@@ -6921,50 +4389,22 @@
       <c r="Z160" s="4"/>
     </row>
     <row r="161" spans="1:26">
-      <c r="A161" s="19">
-        <v>46131</v>
-      </c>
-      <c r="B161" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C161" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="D161" s="10">
-        <v>90.92</v>
-      </c>
-      <c r="E161" s="10">
-        <v>0.35</v>
-      </c>
-      <c r="F161" s="10">
-        <v>91.27</v>
-      </c>
-      <c r="G161" s="10">
-        <v>0</v>
-      </c>
+      <c r="A161" s="19"/>
+      <c r="B161" s="6"/>
+      <c r="C161" s="6"/>
+      <c r="D161" s="10"/>
+      <c r="E161" s="10"/>
+      <c r="F161" s="10"/>
+      <c r="G161" s="10"/>
     </row>
     <row r="162" spans="1:26">
-      <c r="A162" s="18">
-        <v>46131</v>
-      </c>
-      <c r="B162" s="12" t="s">
-        <v>51</v>
-      </c>
-      <c r="C162" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="D162" s="14">
-        <v>91.4</v>
-      </c>
-      <c r="E162" s="16">
-        <v>0</v>
-      </c>
-      <c r="F162" s="14">
-        <v>91.4</v>
-      </c>
-      <c r="G162" s="16">
-        <v>0</v>
-      </c>
+      <c r="A162" s="18"/>
+      <c r="B162" s="12"/>
+      <c r="C162" s="12"/>
+      <c r="D162" s="14"/>
+      <c r="E162" s="16"/>
+      <c r="F162" s="14"/>
+      <c r="G162" s="16"/>
       <c r="H162" s="17"/>
       <c r="I162" s="4"/>
       <c r="J162" s="4"/>
@@ -6986,27 +4426,13 @@
       <c r="Z162" s="4"/>
     </row>
     <row r="163" spans="1:26">
-      <c r="A163" s="5">
-        <v>46132</v>
-      </c>
-      <c r="B163" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C163" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="D163" s="7">
-        <v>16.95</v>
-      </c>
-      <c r="E163" s="7">
-        <v>1.28</v>
-      </c>
-      <c r="F163" s="7">
-        <v>18.25</v>
-      </c>
-      <c r="G163" s="7">
-        <v>0</v>
-      </c>
+      <c r="A163" s="5"/>
+      <c r="B163" s="6"/>
+      <c r="C163" s="6"/>
+      <c r="D163" s="7"/>
+      <c r="E163" s="7"/>
+      <c r="F163" s="7"/>
+      <c r="G163" s="7"/>
       <c r="H163" s="6"/>
       <c r="I163" s="4"/>
       <c r="J163" s="4"/>
@@ -7028,27 +4454,13 @@
       <c r="Z163" s="4"/>
     </row>
     <row r="164" spans="1:26">
-      <c r="A164" s="5">
-        <v>46132</v>
-      </c>
-      <c r="B164" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="C164" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="D164" s="7">
-        <v>80</v>
-      </c>
-      <c r="E164" s="7">
-        <v>0</v>
-      </c>
-      <c r="F164" s="7">
-        <v>100</v>
-      </c>
-      <c r="G164" s="7">
-        <v>20</v>
-      </c>
+      <c r="A164" s="5"/>
+      <c r="B164" s="6"/>
+      <c r="C164" s="6"/>
+      <c r="D164" s="7"/>
+      <c r="E164" s="7"/>
+      <c r="F164" s="7"/>
+      <c r="G164" s="7"/>
       <c r="H164" s="6"/>
       <c r="I164" s="4"/>
       <c r="J164" s="4"/>
@@ -7070,27 +4482,13 @@
       <c r="Z164" s="4"/>
     </row>
     <row r="165" spans="1:26">
-      <c r="A165" s="5">
-        <v>46133</v>
-      </c>
-      <c r="B165" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C165" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="D165" s="7">
-        <v>13.49</v>
-      </c>
-      <c r="E165" s="7">
-        <v>0</v>
-      </c>
-      <c r="F165" s="7">
-        <v>13.49</v>
-      </c>
-      <c r="G165" s="7">
-        <v>0</v>
-      </c>
+      <c r="A165" s="5"/>
+      <c r="B165" s="6"/>
+      <c r="C165" s="6"/>
+      <c r="D165" s="7"/>
+      <c r="E165" s="7"/>
+      <c r="F165" s="7"/>
+      <c r="G165" s="7"/>
       <c r="H165" s="6"/>
       <c r="I165" s="4"/>
       <c r="J165" s="4"/>
@@ -7112,27 +4510,13 @@
       <c r="Z165" s="4"/>
     </row>
     <row r="166" spans="1:26">
-      <c r="A166" s="15">
-        <v>46134</v>
-      </c>
-      <c r="B166" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="C166" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="D166" s="16">
-        <v>103.66</v>
-      </c>
-      <c r="E166" s="16">
-        <v>0</v>
-      </c>
-      <c r="F166" s="16">
-        <v>103.66</v>
-      </c>
-      <c r="G166" s="16">
-        <v>0</v>
-      </c>
+      <c r="A166" s="15"/>
+      <c r="B166" s="12"/>
+      <c r="C166" s="12"/>
+      <c r="D166" s="16"/>
+      <c r="E166" s="16"/>
+      <c r="F166" s="16"/>
+      <c r="G166" s="16"/>
       <c r="H166" s="17"/>
       <c r="I166" s="4"/>
       <c r="J166" s="4"/>
@@ -7154,27 +4538,13 @@
       <c r="Z166" s="4"/>
     </row>
     <row r="167" spans="1:26">
-      <c r="A167" s="5">
-        <v>46135</v>
-      </c>
-      <c r="B167" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C167" s="6" t="s">
-        <v>107</v>
-      </c>
-      <c r="D167" s="7">
-        <v>21.66</v>
-      </c>
-      <c r="E167" s="7">
-        <v>1.65</v>
-      </c>
-      <c r="F167" s="7">
-        <v>23.31</v>
-      </c>
-      <c r="G167" s="7">
-        <v>0</v>
-      </c>
+      <c r="A167" s="5"/>
+      <c r="B167" s="6"/>
+      <c r="C167" s="6"/>
+      <c r="D167" s="7"/>
+      <c r="E167" s="7"/>
+      <c r="F167" s="7"/>
+      <c r="G167" s="7"/>
       <c r="H167" s="6"/>
       <c r="I167" s="4"/>
       <c r="J167" s="4"/>
@@ -7196,27 +4566,13 @@
       <c r="Z167" s="4"/>
     </row>
     <row r="168" spans="1:26">
-      <c r="A168" s="5">
-        <v>46137</v>
-      </c>
-      <c r="B168" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C168" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="D168" s="7">
-        <v>21.87</v>
-      </c>
-      <c r="E168" s="7">
-        <v>1.64</v>
-      </c>
-      <c r="F168" s="7">
-        <v>27.74</v>
-      </c>
-      <c r="G168" s="7">
-        <v>4.2300000000000004</v>
-      </c>
+      <c r="A168" s="5"/>
+      <c r="B168" s="6"/>
+      <c r="C168" s="6"/>
+      <c r="D168" s="7"/>
+      <c r="E168" s="7"/>
+      <c r="F168" s="7"/>
+      <c r="G168" s="7"/>
       <c r="H168" s="6"/>
       <c r="I168" s="4"/>
       <c r="J168" s="4"/>
@@ -7238,27 +4594,13 @@
       <c r="Z168" s="4"/>
     </row>
     <row r="169" spans="1:26">
-      <c r="A169" s="11">
-        <v>46138</v>
-      </c>
-      <c r="B169" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="C169" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="D169" s="7">
-        <v>420.95</v>
-      </c>
-      <c r="E169" s="7">
-        <v>0</v>
-      </c>
-      <c r="F169" s="7">
-        <v>420.95</v>
-      </c>
-      <c r="G169" s="7">
-        <v>0</v>
-      </c>
+      <c r="A169" s="11"/>
+      <c r="B169" s="6"/>
+      <c r="C169" s="6"/>
+      <c r="D169" s="7"/>
+      <c r="E169" s="7"/>
+      <c r="F169" s="7"/>
+      <c r="G169" s="7"/>
       <c r="H169" s="6"/>
       <c r="I169" s="4"/>
       <c r="J169" s="4"/>
@@ -7280,27 +4622,13 @@
       <c r="Z169" s="4"/>
     </row>
     <row r="170" spans="1:26">
-      <c r="A170" s="11">
-        <v>46139</v>
-      </c>
-      <c r="B170" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C170" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="D170" s="7">
-        <v>108.56</v>
-      </c>
-      <c r="E170" s="7">
-        <v>1.46</v>
-      </c>
-      <c r="F170" s="7">
-        <v>110.02</v>
-      </c>
-      <c r="G170" s="7">
-        <v>0</v>
-      </c>
+      <c r="A170" s="11"/>
+      <c r="B170" s="6"/>
+      <c r="C170" s="6"/>
+      <c r="D170" s="7"/>
+      <c r="E170" s="7"/>
+      <c r="F170" s="7"/>
+      <c r="G170" s="7"/>
       <c r="H170" s="6"/>
       <c r="I170" s="4"/>
       <c r="J170" s="4"/>
@@ -7322,27 +4650,13 @@
       <c r="Z170" s="4"/>
     </row>
     <row r="171" spans="1:26">
-      <c r="A171" s="11">
-        <v>46141</v>
-      </c>
-      <c r="B171" s="12" t="s">
-        <v>102</v>
-      </c>
-      <c r="C171" s="12" t="s">
-        <v>108</v>
-      </c>
-      <c r="D171" s="10">
-        <v>30</v>
-      </c>
-      <c r="E171" s="7">
-        <v>0</v>
-      </c>
-      <c r="F171" s="7">
-        <v>30</v>
-      </c>
-      <c r="G171" s="10">
-        <v>0</v>
-      </c>
+      <c r="A171" s="11"/>
+      <c r="B171" s="12"/>
+      <c r="C171" s="12"/>
+      <c r="D171" s="10"/>
+      <c r="E171" s="7"/>
+      <c r="F171" s="7"/>
+      <c r="G171" s="10"/>
       <c r="H171" s="17"/>
       <c r="I171" s="4"/>
       <c r="J171" s="4"/>
@@ -7364,27 +4678,13 @@
       <c r="Z171" s="4"/>
     </row>
     <row r="172" spans="1:26">
-      <c r="A172" s="15">
-        <v>46142</v>
-      </c>
-      <c r="B172" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="C172" s="12" t="s">
-        <v>50</v>
-      </c>
-      <c r="D172" s="16">
-        <v>93</v>
-      </c>
-      <c r="E172" s="16">
-        <v>0</v>
-      </c>
-      <c r="F172" s="16">
-        <v>93</v>
-      </c>
-      <c r="G172" s="16">
-        <v>0</v>
-      </c>
+      <c r="A172" s="15"/>
+      <c r="B172" s="12"/>
+      <c r="C172" s="12"/>
+      <c r="D172" s="16"/>
+      <c r="E172" s="16"/>
+      <c r="F172" s="16"/>
+      <c r="G172" s="16"/>
       <c r="H172" s="17"/>
       <c r="I172" s="4"/>
       <c r="J172" s="4"/>
@@ -7406,27 +4706,13 @@
       <c r="Z172" s="4"/>
     </row>
     <row r="173" spans="1:26">
-      <c r="A173" s="5">
-        <v>46143</v>
-      </c>
-      <c r="B173" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="C173" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="D173" s="7">
-        <v>20</v>
-      </c>
-      <c r="E173" s="7">
-        <v>0</v>
-      </c>
-      <c r="F173" s="7">
-        <v>20</v>
-      </c>
-      <c r="G173" s="7">
-        <v>0</v>
-      </c>
+      <c r="A173" s="5"/>
+      <c r="B173" s="6"/>
+      <c r="C173" s="6"/>
+      <c r="D173" s="7"/>
+      <c r="E173" s="7"/>
+      <c r="F173" s="7"/>
+      <c r="G173" s="7"/>
       <c r="H173" s="6"/>
       <c r="I173" s="4"/>
       <c r="J173" s="4"/>
@@ -7448,27 +4734,13 @@
       <c r="Z173" s="4"/>
     </row>
     <row r="174" spans="1:26">
-      <c r="A174" s="5">
-        <v>46143</v>
-      </c>
-      <c r="B174" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C174" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="D174" s="7">
-        <v>28.07</v>
-      </c>
-      <c r="E174" s="7">
-        <v>2.11</v>
-      </c>
-      <c r="F174" s="7">
-        <v>30.18</v>
-      </c>
-      <c r="G174" s="7">
-        <v>0</v>
-      </c>
+      <c r="A174" s="5"/>
+      <c r="B174" s="6"/>
+      <c r="C174" s="6"/>
+      <c r="D174" s="7"/>
+      <c r="E174" s="7"/>
+      <c r="F174" s="7"/>
+      <c r="G174" s="7"/>
       <c r="H174" s="6"/>
       <c r="I174" s="4"/>
       <c r="J174" s="4"/>
@@ -7490,27 +4762,13 @@
       <c r="Z174" s="4"/>
     </row>
     <row r="175" spans="1:26">
-      <c r="A175" s="11">
-        <v>46144</v>
-      </c>
-      <c r="B175" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="C175" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="D175" s="14">
-        <v>28.29</v>
-      </c>
-      <c r="E175" s="7">
-        <v>0</v>
-      </c>
-      <c r="F175" s="14">
-        <v>28.29</v>
-      </c>
-      <c r="G175" s="7">
-        <v>0</v>
-      </c>
+      <c r="A175" s="11"/>
+      <c r="B175" s="12"/>
+      <c r="C175" s="13"/>
+      <c r="D175" s="14"/>
+      <c r="E175" s="7"/>
+      <c r="F175" s="14"/>
+      <c r="G175" s="7"/>
       <c r="H175" s="6"/>
       <c r="I175" s="4"/>
       <c r="J175" s="4"/>
@@ -7532,27 +4790,13 @@
       <c r="Z175" s="4"/>
     </row>
     <row r="176" spans="1:26">
-      <c r="A176" s="11">
-        <v>46146</v>
-      </c>
-      <c r="B176" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="C176" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="D176" s="14">
-        <v>36</v>
-      </c>
-      <c r="E176" s="7">
-        <v>0</v>
-      </c>
-      <c r="F176" s="14">
-        <v>36</v>
-      </c>
-      <c r="G176" s="7">
-        <v>0</v>
-      </c>
+      <c r="A176" s="11"/>
+      <c r="B176" s="6"/>
+      <c r="C176" s="6"/>
+      <c r="D176" s="14"/>
+      <c r="E176" s="7"/>
+      <c r="F176" s="14"/>
+      <c r="G176" s="7"/>
       <c r="H176" s="6"/>
       <c r="I176" s="4"/>
       <c r="J176" s="4"/>

--- a/expense_dashboard/input/ExpenseTracker.xlsx
+++ b/expense_dashboard/input/ExpenseTracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ws_openai\codex_projects\expense_dashboard\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D4E9544-DC36-4820-B019-9ADD51C60890}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F695A7C2-6F73-4332-AD90-1DA2A7FA5B77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/expense_dashboard/input/ExpenseTracker.xlsx
+++ b/expense_dashboard/input/ExpenseTracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ws_openai\codex_projects\expense_dashboard\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F695A7C2-6F73-4332-AD90-1DA2A7FA5B77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D0C4E0C-724B-4B7A-A164-CD4B1C72DC72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
